--- a/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者Excelデータ取込画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者Excelデータ取込画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1365,20 +1365,88 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-07：取込を紙版/電子版の2モードに分離。購読種別を Excel 列から撤去し画面ラジオ（紙版/電子版）の top-level パラメータに変更（49→48列）。TC-016-023 を top-level `@IsIn([1,2])` 防御確認に、TC-016-031 を電子版ラジオ選択前提に更新。必須列リスト・列数(48)・購読種別チェックボックス言及を全 TC で修正。</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8530,7 +8598,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">49列すべてのチェックボックスが表示されていること、新規登録モードでは必須列（`dokusya_shubetsu`／`tetsuzuki_shurui`／`kanri_shiten_id`／`dokusya_busu`／`tanka_id`／`yubin_no`／`todofuken_code`／`shikuchoson`／`chome_banchi`／`renrakusaki_1`／`hanbaiten_id`／`shiharai_hoho`／`dokusya_kaishi_date`）が無効（非活性）かつチェック済みであること
+            <t xml:space="preserve">48列すべてのチェックボックスが表示されていること、新規登録モードでは必須列（`tetsuzuki_shurui`／`kanri_shiten_id`／`dokusya_busu`／`tanka_id`／`yubin_no`／`todofuken_code`／`shikuchoson`／`chome_banchi`／`renrakusaki_1`／`hanbaiten_id`／`shiharai_hoho`／`dokusya_kaishi_date`）が無効（非活性）かつチェック済みであること
 </t>
           </r>
           <r>
@@ -8835,7 +8903,7 @@
       <c r="D21" s="11" t="n"/>
       <c r="E21" s="46" t="inlineStr">
         <is>
-          <t>取込列パネル — 49列チェックボックスの表示確認</t>
+          <t>取込列パネル — 48列チェックボックスの表示確認</t>
         </is>
       </c>
       <c r="F21" s="10" t="n"/>
@@ -8930,7 +8998,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">取込列パネルが表示されること、全49列のチェックボックスが表示されること
+            <t xml:space="preserve">取込列パネルが表示されること、全48列のチェックボックスが表示されること
 </t>
           </r>
           <r>
@@ -8947,7 +9015,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">新規登録モードでは必須列（`dokusya_shubetsu`／`tetsuzuki_shurui`／`kanri_shiten_id`／`dokusya_busu`／`tanka_id`／`yubin_no`／`todofuken_code`／`shikuchoson`／`chome_banchi`／`renrakusaki_1`／`hanbaiten_id`／`shiharai_hoho`／`dokusya_kaishi_date`）が無効かつチェック済みで表示されていること
+            <t xml:space="preserve">新規登録モードでは必須列（`tetsuzuki_shurui`／`kanri_shiten_id`／`dokusya_busu`／`tanka_id`／`yubin_no`／`todofuken_code`／`shikuchoson`／`chome_banchi`／`renrakusaki_1`／`hanbaiten_id`／`shiharai_hoho`／`dokusya_kaishi_date`）が無効かつチェック済みで表示されていること
 </t>
           </r>
           <r>
@@ -8981,7 +9049,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・列順序はテンプレートファイル（49列固定）と一致すること
+            <t xml:space="preserve">・列順序はテンプレートファイル（48列固定）と一致すること
 </t>
           </r>
           <r>
@@ -10606,7 +10674,7 @@
         <is>
           <t>・role: JA_HONTEN
 ・ログイン済 + MFA認証済
-・テストファイル：購読者3行を含む `.xlsx`、シート名「購読者」、49列ヘッダ</t>
+・テストファイル：購読者3行を含む `.xlsx`、シート名「購読者」、48列ヘッダ</t>
         </is>
       </c>
       <c r="K31" s="10" t="n"/>
@@ -11041,7 +11109,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">プレビュー初期表示で全49列が表示されていることを確認
+            <t xml:space="preserve">プレビュー初期表示で全48列が表示されていることを確認
 </t>
           </r>
           <r>
@@ -11101,7 +11169,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">プレビューに49列分のヘッダと3行のデータが表示されること
+            <t xml:space="preserve">プレビューに48列分のヘッダと3行のデータが表示されること
 </t>
           </r>
           <r>
@@ -11279,7 +11347,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">取込列パネルで購読種別（`dokusya_shubetsu`）など必須列のチェックボックスを操作
+            <t xml:space="preserve">取込列パネルで備考（`biko`）など任意列のチェックボックスを操作（購読種別は画面ラジオの単一ソースで列に無い・v1.6）
 </t>
           </r>
           <r>
@@ -11373,7 +11441,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・新規登録モードの必須列：`dokusya_shubetsu`／`tetsuzuki_shurui`／`kanri_shiten_id`／`dokusya_busu`／`tanka_id`／`yubin_no`／`todofuken_code`／`shikuchoson`／`chome_banchi`／`renrakusaki_1`／`hanbaiten_id`／`shiharai_hoho`／`dokusya_kaishi_date`
+            <t xml:space="preserve">・新規登録モードの必須列：`tetsuzuki_shurui`／`kanri_shiten_id`／`dokusya_busu`／`tanka_id`／`yubin_no`／`todofuken_code`／`shikuchoson`／`chome_banchi`／`renrakusaki_1`／`hanbaiten_id`／`shiharai_hoho`／`dokusya_kaishi_date`
 </t>
           </r>
           <r>
@@ -12033,7 +12101,7 @@
       <c r="BP37" s="10" t="n"/>
       <c r="BQ37" s="11" t="n"/>
     </row>
-    <row r="38" ht="368" customHeight="1">
+    <row r="38" ht="320" customHeight="1">
       <c r="A38" s="44" t="n">
         <v>23</v>
       </c>
@@ -12046,7 +12114,7 @@
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="46" t="inlineStr">
         <is>
-          <t>購読種別=3（併読）はExcel取込不可</t>
+          <t>購読種別=3（併読）はExcel取込不可（top-level・v1.6）</t>
         </is>
       </c>
       <c r="F38" s="10" t="n"/>
@@ -12057,7 +12125,7 @@
         <is>
           <t>・role: JA_HONTEN（ja_id=1）
 ・ログイン済 + MFA認証済
-・テストファイル：`dokusya_shubetsu`=3（併読）の行を含むファイル</t>
+・購読種別は画面ラジオ（紙版/電子版）で一律指定する top-level パラメータ（v1.6）。UI では併読はラジオに出さないため選択不可。API 直呼びで `dokusya_shubetsu`=3 を送った場合の防御確認。</t>
         </is>
       </c>
       <c r="K38" s="10" t="n"/>
@@ -12082,7 +12150,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">ファイルアップロード、取込モード「新規登録」
+            <t xml:space="preserve">画面上：購読種別ラジオに 併読 の選択肢が表示されないこと（紙版 / 電子版 のみ）を確認する。
 </t>
           </r>
           <r>
@@ -12099,7 +12167,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>取込開始ボタン押下 → 確認ダイアログ「実行」</t>
+            <t>API 直呼びで top-level `dokusya_shubetsu`=3（併読）を送信する。</t>
           </r>
         </is>
       </c>
@@ -12125,7 +12193,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">プレビューが表示されること
+            <t xml:space="preserve">購読種別ラジオは 紙版 / 電子版 の2択のみで、併読は選べないこと。
 </t>
           </r>
           <r>
@@ -12142,7 +12210,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: IMPORT_VALIDATION_ERROR`）、`errors` 配列に `{ row: N, field: 'dokusya_shubetsu', message: '併読はExcel取込できません' }` 相当が含まれること、トースト `取込み処理にエラーが発生しました。「行{N}: {項目名} — {エラー理由}」` が表示されること（ACSMS-MSG-016-005）、全件ロールバックされ DB に登録されないこと
+            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: VALIDATION_ERROR`、`errors` に `{ field: 'dokusya_shubetsu' }` を含む — DTO `@IsIn([1,2])`）、DB に登録されないこと。
 </t>
           </r>
           <r>
@@ -12159,7 +12227,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・購読種別=3（併読）は画面取込の対象外（業務ルール）
+            <t xml:space="preserve">・購読種別=3（併読）は画面取込の対象外（業務ルール・第3システム同期のため読取専用）
 </t>
           </r>
           <r>
@@ -12652,7 +12720,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">シート名が「購読者」であること、1行目に49列のヘッダーが含まれていること
+            <t xml:space="preserve">シート名が「購読者」であること、1行目に48列のヘッダーが含まれていること
 </t>
           </r>
           <r>
@@ -12669,7 +12737,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・列順は `screen-design.md §3.1` および `api.md §テンプレートファイル仕様` に従う（49列固定）</t>
+            <t>・列順は `screen-design.md §3.1` および `api.md §テンプレートファイル仕様` に従う（48列固定）</t>
           </r>
         </is>
       </c>
@@ -12736,7 +12804,7 @@
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="46" t="inlineStr">
         <is>
-          <t>テンプレート — 49列ヘッダーの順序・列数確認</t>
+          <t>テンプレート — 48列ヘッダーの順序・列数確認</t>
         </is>
       </c>
       <c r="F42" s="10" t="n"/>
@@ -12789,7 +12857,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>49列分のヘッダー文字列と列数を確認</t>
+            <t>48列分のヘッダー文字列と列数を確認</t>
           </r>
         </is>
       </c>
@@ -12815,7 +12883,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">シート「購読者」の1行目に49列のヘッダーが表示されていること
+            <t xml:space="preserve">シート「購読者」の1行目に48列のヘッダーが表示されていること
 </t>
           </r>
           <r>
@@ -12832,7 +12900,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">ヘッダーが `screen-design.md §画面項目定義` および `api.md §テンプレートファイル仕様` の定義順で並んでいること、列数がちょうど49列であること
+            <t xml:space="preserve">ヘッダーが `screen-design.md §画面項目定義` および `api.md §テンプレートファイル仕様` の定義順で並んでいること、列数がちょうど48列であること
 </t>
           </r>
           <r>
@@ -13283,7 +13351,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード200が返却されること、レスポンスは `import_mode: "NEW"`, `created_count: 3`、トースト `正常に取り込みました。` が表示されること（ACSMS-MSG-016-004）、取込件数がトーストで表示されること
+            <t xml:space="preserve">HTTPステータスコード200が返却されること、レスポンスは `import_mode: "NEW"`, `created_count: 3`、トースト `取り込みました。` が表示されること（ACSMS-MSG-016-004）、取込件数がトーストで表示されること
 </t>
           </r>
           <r>
@@ -13871,7 +13939,8 @@
       <c r="J48" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=1）
-・テストファイル：`dokusya_shubetsu`=2（電子版）かつ `shiharai_hoho`=クレジットカードの行を含むファイル</t>
+・購読種別ラジオ＝電子版（top-level `dokusya_shubetsu`=2・v1.6）
+・テストファイル：`shiharai_hoho`=クレジットカードの行を含むファイル</t>
         </is>
       </c>
       <c r="K48" s="10" t="n"/>
@@ -13896,7 +13965,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">ファイルアップロード、取込モード「新規登録」
+            <t xml:space="preserve">購読種別ラジオ「電子版」を選択し、ファイルアップロード、取込モード「新規登録」
 </t>
           </r>
           <r>
@@ -14867,7 +14936,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード200が返却されること、`import_mode: "UPDATE_ALL"`, `updated_count: 1`、トースト `正常に取り込みました。` が表示されること（ACSMS-MSG-016-004）
+            <t xml:space="preserve">HTTPステータスコード200が返却されること、`import_mode: "UPDATE_ALL"`, `updated_count: 1`、トースト `取り込みました。` が表示されること（ACSMS-MSG-016-004）
 </t>
           </r>
           <r>
@@ -15455,7 +15524,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード200が返却されること、`updated_count: 1`、トースト `正常に取り込みました。` が表示されること（ACSMS-MSG-016-004）
+            <t xml:space="preserve">HTTPステータスコード200が返却されること、`updated_count: 1`、トースト `取り込みました。` が表示されること（ACSMS-MSG-016-004）
 </t>
           </r>
           <r>
@@ -15778,7 +15847,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード200が返却されること、`import_mode: "UPDATE_PARTIAL"`, `updated_count: 1`、トースト `正常に取り込みました。` が表示されること（ACSMS-MSG-016-004）
+            <t xml:space="preserve">HTTPステータスコード200が返却されること、`import_mode: "UPDATE_PARTIAL"`, `updated_count: 1`、トースト `取り込みました。` が表示されること（ACSMS-MSG-016-004）
 </t>
           </r>
           <r>
@@ -16213,7 +16282,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード200が返却されること、`updated_count: 1`、トースト `正常に取り込みました。` が表示されること（ACSMS-MSG-016-004）
+            <t xml:space="preserve">HTTPステータスコード200が返却されること、`updated_count: 1`、トースト `取り込みました。` が表示されること（ACSMS-MSG-016-004）
 </t>
           </r>
           <r>
@@ -16792,7 +16861,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・`import_mode` は `NEW` / `UPDATE_ALL` / `UPDATE_PARTIAL` のみ許容、`selected_columns` は1〜49の物理カラム名配列で必須</t>
+            <t>・`import_mode` は `NEW` / `UPDATE_ALL` / `UPDATE_PARTIAL` のみ許容、`selected_columns` は1〜48の物理カラム名配列で必須</t>
           </r>
         </is>
       </c>

--- a/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者Excelデータ取込画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者Excelデータ取込画面_v1.0.xlsx
@@ -6370,7 +6370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ71"/>
+  <dimension ref="A1:BQ75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -18208,8 +18208,1276 @@
       <c r="BP71" s="10" t="n"/>
       <c r="BQ71" s="11" t="n"/>
     </row>
+    <row r="72" ht="450" customHeight="1">
+      <c r="A72" s="44" t="n">
+        <v>52</v>
+      </c>
+      <c r="B72" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-016-052</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="11" t="n"/>
+      <c r="E72" s="46" t="inlineStr">
+        <is>
+          <t>適用日／中止日 — 画面入力・相互排他・モード別の可否</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="11" t="n"/>
+      <c r="J72" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（`dokusya.import` 保有）
+・テンプレートをダウンロード済み（46列）</t>
+        </is>
+      </c>
+      <c r="K72" s="10" t="n"/>
+      <c r="L72" s="10" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="11" t="n"/>
+      <c r="Q72" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">テンプレートのヘッダー行を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">取込モード＝新規登録 の状態で「読者情報変更適用日」「購読中止日」の入力欄を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">取込モード＝更新 に切り替え、読者情報変更適用日に未来日を入力する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">続けて購読中止日に日付を入力しようとする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">読者情報変更適用日を空にしてから購読中止日に日付を入力する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>更新モードで両方とも空のまま「取込開始」をクリックする</t>
+          </r>
+        </is>
+      </c>
+      <c r="R72" s="10" t="n"/>
+      <c r="S72" s="10" t="n"/>
+      <c r="T72" s="10" t="n"/>
+      <c r="U72" s="10" t="n"/>
+      <c r="V72" s="10" t="n"/>
+      <c r="W72" s="11" t="n"/>
+      <c r="X72" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「読者情報変更適用日」「購読中止日」の列が**存在しないこと**（46列。購読種別も無い）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">両方の入力欄が非活性であること（新規登録に変更適用日・中止日の概念が無い）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">入力できること。購読中止日の入力欄が非活性になること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">購読中止日が入力できないこと（相互排他）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">購読中止日が入力でき、読者情報変更適用日が非活性になること。ACSMS-MSG-016-014 が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ACSMS-MSG-016-008 が表示され、APIが呼ばれないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・DevTools で両方を同時に送った場合は 400（`VALIDATION_ERROR` / ACSMS-MSG-016-007）が返ること。画面の抑止は境界ではなくBEでも弾く
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・新規登録でどちらかを送った場合は 400（ACSMS-MSG-016-009 / ACSMS-MSG-016-010）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y72" s="10" t="n"/>
+      <c r="Z72" s="10" t="n"/>
+      <c r="AA72" s="10" t="n"/>
+      <c r="AB72" s="10" t="n"/>
+      <c r="AC72" s="10" t="n"/>
+      <c r="AD72" s="11" t="n"/>
+      <c r="AE72" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF72" s="11" t="n"/>
+      <c r="AG72" s="45" t="inlineStr"/>
+      <c r="AH72" s="10" t="n"/>
+      <c r="AI72" s="11" t="n"/>
+      <c r="AJ72" s="45" t="inlineStr"/>
+      <c r="AK72" s="10" t="n"/>
+      <c r="AL72" s="11" t="n"/>
+      <c r="AM72" s="45" t="inlineStr"/>
+      <c r="AN72" s="10" t="n"/>
+      <c r="AO72" s="11" t="n"/>
+      <c r="AP72" s="45" t="inlineStr"/>
+      <c r="AQ72" s="10" t="n"/>
+      <c r="AR72" s="11" t="n"/>
+      <c r="AS72" s="45" t="inlineStr"/>
+      <c r="AT72" s="10" t="n"/>
+      <c r="AU72" s="11" t="n"/>
+      <c r="AV72" s="45" t="inlineStr"/>
+      <c r="AW72" s="10" t="n"/>
+      <c r="AX72" s="11" t="n"/>
+      <c r="AY72" s="45" t="inlineStr"/>
+      <c r="AZ72" s="10" t="n"/>
+      <c r="BA72" s="11" t="n"/>
+      <c r="BB72" s="45" t="inlineStr"/>
+      <c r="BC72" s="10" t="n"/>
+      <c r="BD72" s="11" t="n"/>
+      <c r="BE72" s="45" t="inlineStr"/>
+      <c r="BF72" s="10" t="n"/>
+      <c r="BG72" s="11" t="n"/>
+      <c r="BH72" s="45" t="inlineStr"/>
+      <c r="BI72" s="10" t="n"/>
+      <c r="BJ72" s="11" t="n"/>
+      <c r="BK72" s="46" t="inlineStr"/>
+      <c r="BL72" s="10" t="n"/>
+      <c r="BM72" s="10" t="n"/>
+      <c r="BN72" s="10" t="n"/>
+      <c r="BO72" s="10" t="n"/>
+      <c r="BP72" s="10" t="n"/>
+      <c r="BQ72" s="11" t="n"/>
+    </row>
+    <row r="73" ht="450" customHeight="1">
+      <c r="A73" s="44" t="n">
+        <v>53</v>
+      </c>
+      <c r="B73" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-016-053</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="n"/>
+      <c r="D73" s="11" t="n"/>
+      <c r="E73" s="46" t="inlineStr">
+        <is>
+          <t>更新 — 購読種別ごとの適用日ルールと帳票影響項目のロック</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
+      <c r="H73" s="10" t="n"/>
+      <c r="I73" s="11" t="n"/>
+      <c r="J73" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・事前データ：紙版・電子版の既存購読者（購読開始日は過去日）</t>
+        </is>
+      </c>
+      <c r="K73" s="10" t="n"/>
+      <c r="L73" s="10" t="n"/>
+      <c r="M73" s="10" t="n"/>
+      <c r="N73" s="10" t="n"/>
+      <c r="O73" s="10" t="n"/>
+      <c r="P73" s="11" t="n"/>
+      <c r="Q73" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">更新モード × 電子版 を選び、読者情報変更適用日の入力欄を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">更新モード × 紙版 に切り替え、読者情報変更適用日に**当日**を入力する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">取込列パネルで 購読部数 / 販売店コード / 郵便番号 のチェックボックスを確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">読者情報変更適用日を**未来日**に変更する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>当日を指定したまま DevTools で `selected_columns` に `hanbaiten_code` を含めて送信する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R73" s="10" t="n"/>
+      <c r="S73" s="10" t="n"/>
+      <c r="T73" s="10" t="n"/>
+      <c r="U73" s="10" t="n"/>
+      <c r="V73" s="10" t="n"/>
+      <c r="W73" s="11" t="n"/>
+      <c r="X73" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">入力欄に当日が表示され、非活性であること。ACSMS-MSG-016-012 が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">入力できること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">帳票影響項目12列（購読部数・販売店コード・購読者住所4項目・配達先住所5項目）が選択できないこと。ACSMS-MSG-016-013 が表示されること。備考など帳票に影響しない列は選択できること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">帳票影響項目が選択可能に戻ること（＝予約変更）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">400（`IMPORT_VALIDATION_ERROR`）が返り、`errors[].field` が **`hanbaiten_code`**（`hanbaiten_id` ではない）であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・ステップ5は「当日変更で販売店は変えられない」ルールが Excel 経路からすり抜けていた不具合の回帰確認。取込行は販売店をコードで持つため、単票 dto の `hanbaiten_id` のままでは変更が検出されなかった
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・選択した帳票影響項目の値が既存と同じ場合は「変更なし」として 200 になること（既存値ロード漏れの回帰確認）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y73" s="10" t="n"/>
+      <c r="Z73" s="10" t="n"/>
+      <c r="AA73" s="10" t="n"/>
+      <c r="AB73" s="10" t="n"/>
+      <c r="AC73" s="10" t="n"/>
+      <c r="AD73" s="11" t="n"/>
+      <c r="AE73" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF73" s="11" t="n"/>
+      <c r="AG73" s="45" t="inlineStr"/>
+      <c r="AH73" s="10" t="n"/>
+      <c r="AI73" s="11" t="n"/>
+      <c r="AJ73" s="45" t="inlineStr"/>
+      <c r="AK73" s="10" t="n"/>
+      <c r="AL73" s="11" t="n"/>
+      <c r="AM73" s="45" t="inlineStr"/>
+      <c r="AN73" s="10" t="n"/>
+      <c r="AO73" s="11" t="n"/>
+      <c r="AP73" s="45" t="inlineStr"/>
+      <c r="AQ73" s="10" t="n"/>
+      <c r="AR73" s="11" t="n"/>
+      <c r="AS73" s="45" t="inlineStr"/>
+      <c r="AT73" s="10" t="n"/>
+      <c r="AU73" s="11" t="n"/>
+      <c r="AV73" s="45" t="inlineStr"/>
+      <c r="AW73" s="10" t="n"/>
+      <c r="AX73" s="11" t="n"/>
+      <c r="AY73" s="45" t="inlineStr"/>
+      <c r="AZ73" s="10" t="n"/>
+      <c r="BA73" s="11" t="n"/>
+      <c r="BB73" s="45" t="inlineStr"/>
+      <c r="BC73" s="10" t="n"/>
+      <c r="BD73" s="11" t="n"/>
+      <c r="BE73" s="45" t="inlineStr"/>
+      <c r="BF73" s="10" t="n"/>
+      <c r="BG73" s="11" t="n"/>
+      <c r="BH73" s="45" t="inlineStr"/>
+      <c r="BI73" s="10" t="n"/>
+      <c r="BJ73" s="11" t="n"/>
+      <c r="BK73" s="46" t="inlineStr"/>
+      <c r="BL73" s="10" t="n"/>
+      <c r="BM73" s="10" t="n"/>
+      <c r="BN73" s="10" t="n"/>
+      <c r="BO73" s="10" t="n"/>
+      <c r="BP73" s="10" t="n"/>
+      <c r="BQ73" s="11" t="n"/>
+    </row>
+    <row r="74" ht="450" customHeight="1">
+      <c r="A74" s="44" t="n">
+        <v>54</v>
+      </c>
+      <c r="B74" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-016-054</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="n"/>
+      <c r="D74" s="11" t="n"/>
+      <c r="E74" s="46" t="inlineStr">
+        <is>
+          <t>一括中止 — 解約予約の作成（紙版・連携なし）</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="n"/>
+      <c r="G74" s="10" t="n"/>
+      <c r="H74" s="10" t="n"/>
+      <c r="I74" s="11" t="n"/>
+      <c r="J74" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・事前データ：紙版の既存購読者（購読中・購読部数=3）</t>
+        </is>
+      </c>
+      <c r="K74" s="10" t="n"/>
+      <c r="L74" s="10" t="n"/>
+      <c r="M74" s="10" t="n"/>
+      <c r="N74" s="10" t="n"/>
+      <c r="O74" s="10" t="n"/>
+      <c r="P74" s="11" t="n"/>
+      <c r="Q74" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">更新モードで購読中止日に未来日を入力する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">取込列パネルを確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「取込開始」→ 確認ダイアログで「はい」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DB 確認: `SELECT dokusya_busu, dokusya_chushi_date, kaiyaku_flg, torikeshi_flg FROM t_dokusya_rireki WHERE dokusya_id = :id ORDER BY rireki_no DESC LIMIT 1`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DB 確認: `SELECT dokusya_chushi_date, tetsuzuki_shurui, dokusya_busu FROM t_dokusya WHERE dokusya_id = :id`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>一覧（SCR-014）で該当行の「購読中止日」列を確認する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R74" s="10" t="n"/>
+      <c r="S74" s="10" t="n"/>
+      <c r="T74" s="10" t="n"/>
+      <c r="U74" s="10" t="n"/>
+      <c r="V74" s="10" t="n"/>
+      <c r="W74" s="11" t="n"/>
+      <c r="X74" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">入力でき、ACSMS-MSG-016-014 が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">チェックボックスがID列だけに縮退していること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ACSMS-MSG-016-004 が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`dokusya_busu=0`・`dokusya_chushi_date=入力日`・`kaiyaku_flg=false`・`torikeshi_flg=false` の予約行が1件追加されていること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`dokusya_chushi_date` が入力日で反映されていること。`tetsuzuki_shurui=1`（購読中のまま＝確定は到来日バッチ）、`dokusya_busu` は元の3のまま（予約は master の部数を変えない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">入力した中止日が表示されていること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・`selected_columns` に他の列を含めて DevTools から送っても、それらの列は更新されないこと（一括中止はキー列のみ）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・紙版は電子版システムへの連携を行わないこと</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y74" s="10" t="n"/>
+      <c r="Z74" s="10" t="n"/>
+      <c r="AA74" s="10" t="n"/>
+      <c r="AB74" s="10" t="n"/>
+      <c r="AC74" s="10" t="n"/>
+      <c r="AD74" s="11" t="n"/>
+      <c r="AE74" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF74" s="11" t="n"/>
+      <c r="AG74" s="45" t="inlineStr"/>
+      <c r="AH74" s="10" t="n"/>
+      <c r="AI74" s="11" t="n"/>
+      <c r="AJ74" s="45" t="inlineStr"/>
+      <c r="AK74" s="10" t="n"/>
+      <c r="AL74" s="11" t="n"/>
+      <c r="AM74" s="45" t="inlineStr"/>
+      <c r="AN74" s="10" t="n"/>
+      <c r="AO74" s="11" t="n"/>
+      <c r="AP74" s="45" t="inlineStr"/>
+      <c r="AQ74" s="10" t="n"/>
+      <c r="AR74" s="11" t="n"/>
+      <c r="AS74" s="45" t="inlineStr"/>
+      <c r="AT74" s="10" t="n"/>
+      <c r="AU74" s="11" t="n"/>
+      <c r="AV74" s="45" t="inlineStr"/>
+      <c r="AW74" s="10" t="n"/>
+      <c r="AX74" s="11" t="n"/>
+      <c r="AY74" s="45" t="inlineStr"/>
+      <c r="AZ74" s="10" t="n"/>
+      <c r="BA74" s="11" t="n"/>
+      <c r="BB74" s="45" t="inlineStr"/>
+      <c r="BC74" s="10" t="n"/>
+      <c r="BD74" s="11" t="n"/>
+      <c r="BE74" s="45" t="inlineStr"/>
+      <c r="BF74" s="10" t="n"/>
+      <c r="BG74" s="11" t="n"/>
+      <c r="BH74" s="45" t="inlineStr"/>
+      <c r="BI74" s="10" t="n"/>
+      <c r="BJ74" s="11" t="n"/>
+      <c r="BK74" s="46" t="inlineStr"/>
+      <c r="BL74" s="10" t="n"/>
+      <c r="BM74" s="10" t="n"/>
+      <c r="BN74" s="10" t="n"/>
+      <c r="BO74" s="10" t="n"/>
+      <c r="BP74" s="10" t="n"/>
+      <c r="BQ74" s="11" t="n"/>
+    </row>
+    <row r="75" ht="450" customHeight="1">
+      <c r="A75" s="44" t="n">
+        <v>55</v>
+      </c>
+      <c r="B75" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-016-055</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="n"/>
+      <c r="D75" s="11" t="n"/>
+      <c r="E75" s="46" t="inlineStr">
+        <is>
+          <t>一括中止 — 電子版の連携失敗で全ロールバック＋打ち消し</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="n"/>
+      <c r="G75" s="10" t="n"/>
+      <c r="H75" s="10" t="n"/>
+      <c r="I75" s="11" t="n"/>
+      <c r="J75" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・事前データ：電子版の既存購読者3件（電子版会員IDあり・非クレカ）
+・電子版連携が有効（DENSHIBAN_PUSH_ENABLED=true）
+・3件目の連携がエラーを返すよう擬似環境を設定</t>
+        </is>
+      </c>
+      <c r="K75" s="10" t="n"/>
+      <c r="L75" s="10" t="n"/>
+      <c r="M75" s="10" t="n"/>
+      <c r="N75" s="10" t="n"/>
+      <c r="O75" s="10" t="n"/>
+      <c r="P75" s="11" t="n"/>
+      <c r="Q75" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">更新モードで購読中止日に未来日を入力し、3件を取込む
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DB 確認: `SELECT COUNT(*) FROM t_dokusya_rireki WHERE dokusya_id IN (:ids) AND dokusya_chushi_date IS NOT NULL`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DB 確認: `SELECT dokusya_chushi_date FROM t_dokusya WHERE dokusya_id IN (:ids)`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">電子版連携ログを確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`t_log` を確認する（`log_type=3`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>501件の電子版一括中止を試行する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R75" s="10" t="n"/>
+      <c r="S75" s="10" t="n"/>
+      <c r="T75" s="10" t="n"/>
+      <c r="U75" s="10" t="n"/>
+      <c r="V75" s="10" t="n"/>
+      <c r="W75" s="11" t="n"/>
+      <c r="X75" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">エラーが表示され、取込が失敗すること（電子版が返した理由が表示されること）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">予約行が**1件も作成されていないこと**（全件ロールバック）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`dokusya_chushi_date` が更新されていないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">1件目・2件目に `action_kbn=cancel` + `cancel_ym=YYYYMM` が送られた後、**同じ2件へ打ち消し（`cancel_ym` 空文字）が送られていること**
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">エラーログが記録されていること。打ち消しにも失敗した場合は、対象の電子版会員IDがメッセージに含まれていること（運用の手動対応用）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">400（`VALIDATION_ERROR` / ACSMS-MSG-016-011）が返り、1件も処理されないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・打ち消しは電子版APIに解約取消の処理区分が無いため `cancel` + 空 `cancel_ym` で行う（顧客判断 2026-08）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・**空 `cancel_ym` を電子版が受理するかは未検証**。拒否される場合、この打ち消しも SCR-014 の予約取消も成立しないため、統合テストではこの項目を最優先で確認すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・紙版は連携が無いため本ケースの対象外（通常の全件ロールバックのみ）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y75" s="10" t="n"/>
+      <c r="Z75" s="10" t="n"/>
+      <c r="AA75" s="10" t="n"/>
+      <c r="AB75" s="10" t="n"/>
+      <c r="AC75" s="10" t="n"/>
+      <c r="AD75" s="11" t="n"/>
+      <c r="AE75" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF75" s="11" t="n"/>
+      <c r="AG75" s="45" t="inlineStr"/>
+      <c r="AH75" s="10" t="n"/>
+      <c r="AI75" s="11" t="n"/>
+      <c r="AJ75" s="45" t="inlineStr"/>
+      <c r="AK75" s="10" t="n"/>
+      <c r="AL75" s="11" t="n"/>
+      <c r="AM75" s="45" t="inlineStr"/>
+      <c r="AN75" s="10" t="n"/>
+      <c r="AO75" s="11" t="n"/>
+      <c r="AP75" s="45" t="inlineStr"/>
+      <c r="AQ75" s="10" t="n"/>
+      <c r="AR75" s="11" t="n"/>
+      <c r="AS75" s="45" t="inlineStr"/>
+      <c r="AT75" s="10" t="n"/>
+      <c r="AU75" s="11" t="n"/>
+      <c r="AV75" s="45" t="inlineStr"/>
+      <c r="AW75" s="10" t="n"/>
+      <c r="AX75" s="11" t="n"/>
+      <c r="AY75" s="45" t="inlineStr"/>
+      <c r="AZ75" s="10" t="n"/>
+      <c r="BA75" s="11" t="n"/>
+      <c r="BB75" s="45" t="inlineStr"/>
+      <c r="BC75" s="10" t="n"/>
+      <c r="BD75" s="11" t="n"/>
+      <c r="BE75" s="45" t="inlineStr"/>
+      <c r="BF75" s="10" t="n"/>
+      <c r="BG75" s="11" t="n"/>
+      <c r="BH75" s="45" t="inlineStr"/>
+      <c r="BI75" s="10" t="n"/>
+      <c r="BJ75" s="11" t="n"/>
+      <c r="BK75" s="46" t="inlineStr"/>
+      <c r="BL75" s="10" t="n"/>
+      <c r="BM75" s="10" t="n"/>
+      <c r="BN75" s="10" t="n"/>
+      <c r="BO75" s="10" t="n"/>
+      <c r="BP75" s="10" t="n"/>
+      <c r="BQ75" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="942">
+  <mergeCells count="1010">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="B60:D60"/>
@@ -18249,7 +19517,10 @@
     <mergeCell ref="AG42:AI42"/>
     <mergeCell ref="BK70:BQ70"/>
     <mergeCell ref="AJ22:AL22"/>
+    <mergeCell ref="AY74:BA74"/>
     <mergeCell ref="AP13:AR13"/>
+    <mergeCell ref="AS74:AU74"/>
+    <mergeCell ref="AV75:AX75"/>
     <mergeCell ref="BK42:BQ42"/>
     <mergeCell ref="Q38:W38"/>
     <mergeCell ref="AE34:AF34"/>
@@ -18257,6 +19528,7 @@
     <mergeCell ref="AP71:AR71"/>
     <mergeCell ref="BK47:BQ47"/>
     <mergeCell ref="E25:I25"/>
+    <mergeCell ref="X74:AD74"/>
     <mergeCell ref="X68:AD68"/>
     <mergeCell ref="AE36:AF36"/>
     <mergeCell ref="AS51:AU51"/>
@@ -18268,11 +19540,14 @@
     <mergeCell ref="BH21:BJ21"/>
     <mergeCell ref="AM34:AO34"/>
     <mergeCell ref="AJ38:AL38"/>
+    <mergeCell ref="AP73:AR73"/>
+    <mergeCell ref="J75:P75"/>
     <mergeCell ref="BE35:BG35"/>
     <mergeCell ref="BK48:BQ48"/>
     <mergeCell ref="AM49:AO49"/>
     <mergeCell ref="AE50:AF50"/>
     <mergeCell ref="X69:AD69"/>
+    <mergeCell ref="B73:D73"/>
     <mergeCell ref="BE22:BG22"/>
     <mergeCell ref="BH23:BJ23"/>
     <mergeCell ref="AE31:AF31"/>
@@ -18286,6 +19561,7 @@
     <mergeCell ref="J39:P39"/>
     <mergeCell ref="X21:AD21"/>
     <mergeCell ref="AE62:AF62"/>
+    <mergeCell ref="B74:D74"/>
     <mergeCell ref="AG47:AI47"/>
     <mergeCell ref="B68:D68"/>
     <mergeCell ref="AF8:AH8"/>
@@ -18313,6 +19589,7 @@
     <mergeCell ref="AS64:AU64"/>
     <mergeCell ref="BE15:BG15"/>
     <mergeCell ref="AP68:AR68"/>
+    <mergeCell ref="Q72:W72"/>
     <mergeCell ref="J65:P65"/>
     <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="BE33:BG33"/>
@@ -18328,6 +19605,7 @@
     <mergeCell ref="Q46:W46"/>
     <mergeCell ref="BH55:BJ55"/>
     <mergeCell ref="AM24:AO24"/>
+    <mergeCell ref="AJ72:AL72"/>
     <mergeCell ref="AG27:AI27"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="AM60:AO60"/>
@@ -18336,6 +19614,7 @@
     <mergeCell ref="W3:AH3"/>
     <mergeCell ref="E33:I33"/>
     <mergeCell ref="Q48:W48"/>
+    <mergeCell ref="AE75:AF75"/>
     <mergeCell ref="AV13:AX13"/>
     <mergeCell ref="BH42:BJ42"/>
     <mergeCell ref="AS17:AU17"/>
@@ -18346,11 +19625,13 @@
     <mergeCell ref="AV53:AX53"/>
     <mergeCell ref="AS19:AU19"/>
     <mergeCell ref="Q56:W56"/>
+    <mergeCell ref="AS75:AU75"/>
     <mergeCell ref="Q43:W43"/>
     <mergeCell ref="J14:P14"/>
     <mergeCell ref="AE39:AF39"/>
     <mergeCell ref="B51:D51"/>
     <mergeCell ref="A18:BQ18"/>
+    <mergeCell ref="E74:I74"/>
     <mergeCell ref="AM50:AO50"/>
     <mergeCell ref="AJ54:AL54"/>
     <mergeCell ref="AM15:AO15"/>
@@ -18384,6 +19665,7 @@
     <mergeCell ref="BK68:BQ68"/>
     <mergeCell ref="A44:BQ44"/>
     <mergeCell ref="AY47:BA47"/>
+    <mergeCell ref="AS72:AU72"/>
     <mergeCell ref="E21:I21"/>
     <mergeCell ref="BH50:BJ50"/>
     <mergeCell ref="Q36:W36"/>
@@ -18410,8 +19692,10 @@
     <mergeCell ref="X27:AD27"/>
     <mergeCell ref="AG66:AI66"/>
     <mergeCell ref="BB46:BD46"/>
+    <mergeCell ref="AM74:AO74"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="AY60:BA60"/>
+    <mergeCell ref="AG74:AI74"/>
     <mergeCell ref="AV15:AX15"/>
     <mergeCell ref="AY16:BA16"/>
     <mergeCell ref="Q62:W62"/>
@@ -18419,6 +19703,7 @@
     <mergeCell ref="BB48:BD48"/>
     <mergeCell ref="AG68:AI68"/>
     <mergeCell ref="AG43:AI43"/>
+    <mergeCell ref="AP72:AR72"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="E49:I49"/>
     <mergeCell ref="J68:P68"/>
@@ -18439,6 +19724,7 @@
     <mergeCell ref="BH47:BJ47"/>
     <mergeCell ref="AS22:AU22"/>
     <mergeCell ref="X20:AD20"/>
+    <mergeCell ref="BH74:BJ74"/>
     <mergeCell ref="X14:AD14"/>
     <mergeCell ref="AY42:BA42"/>
     <mergeCell ref="AE55:AF55"/>
@@ -18460,26 +19746,33 @@
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="BH58:BJ58"/>
     <mergeCell ref="AV28:AX28"/>
+    <mergeCell ref="Q75:W75"/>
     <mergeCell ref="AY48:BA48"/>
     <mergeCell ref="BB49:BD49"/>
     <mergeCell ref="AG62:AI62"/>
     <mergeCell ref="AE33:AF33"/>
     <mergeCell ref="BB36:BD36"/>
+    <mergeCell ref="AV74:AX74"/>
     <mergeCell ref="E31:I31"/>
     <mergeCell ref="AV36:AX36"/>
     <mergeCell ref="T6:V6"/>
     <mergeCell ref="B20:D20"/>
+    <mergeCell ref="AE73:AF73"/>
     <mergeCell ref="Q39:W39"/>
     <mergeCell ref="AS33:AU33"/>
+    <mergeCell ref="AJ75:AL75"/>
     <mergeCell ref="AM36:AO36"/>
     <mergeCell ref="F1:Q1"/>
     <mergeCell ref="AP37:AR37"/>
     <mergeCell ref="J34:P34"/>
     <mergeCell ref="AY37:BA37"/>
     <mergeCell ref="BE65:BG65"/>
+    <mergeCell ref="BK72:BQ72"/>
     <mergeCell ref="AS35:AU35"/>
     <mergeCell ref="J49:P49"/>
+    <mergeCell ref="J74:P74"/>
     <mergeCell ref="AE68:AF68"/>
+    <mergeCell ref="AE74:AF74"/>
     <mergeCell ref="J36:P36"/>
     <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
@@ -18504,8 +19797,11 @@
     <mergeCell ref="Q65:W65"/>
     <mergeCell ref="AY68:BA68"/>
     <mergeCell ref="BH71:BJ71"/>
+    <mergeCell ref="BE75:BG75"/>
+    <mergeCell ref="AG75:AI75"/>
     <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
+    <mergeCell ref="BH73:BJ73"/>
     <mergeCell ref="BK19:BQ19"/>
     <mergeCell ref="AE21:AF21"/>
     <mergeCell ref="X46:AD46"/>
@@ -18535,6 +19831,7 @@
     <mergeCell ref="AG64:AI64"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="J24:P24"/>
+    <mergeCell ref="BB75:BD75"/>
     <mergeCell ref="AG51:AI51"/>
     <mergeCell ref="Q20:W20"/>
     <mergeCell ref="B47:D47"/>
@@ -18579,6 +19876,7 @@
     <mergeCell ref="BK63:BQ63"/>
     <mergeCell ref="AJ15:AL15"/>
     <mergeCell ref="AY67:BA67"/>
+    <mergeCell ref="BB72:BD72"/>
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="AG19:AI19"/>
     <mergeCell ref="X36:AD36"/>
@@ -18601,6 +19899,7 @@
     <mergeCell ref="AG14:AI14"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="AV32:AX32"/>
+    <mergeCell ref="Q73:W73"/>
     <mergeCell ref="E45:I45"/>
     <mergeCell ref="AS29:AU29"/>
     <mergeCell ref="AM42:AO42"/>
@@ -18618,6 +19917,7 @@
     <mergeCell ref="AS31:AU31"/>
     <mergeCell ref="AM71:AO71"/>
     <mergeCell ref="X64:AD64"/>
+    <mergeCell ref="AG72:AI72"/>
     <mergeCell ref="J32:P32"/>
     <mergeCell ref="J63:P63"/>
     <mergeCell ref="AY38:BA38"/>
@@ -18638,6 +19938,7 @@
     <mergeCell ref="B69:D69"/>
     <mergeCell ref="A61:BQ61"/>
     <mergeCell ref="AP59:AR59"/>
+    <mergeCell ref="E73:I73"/>
     <mergeCell ref="AP46:AR46"/>
     <mergeCell ref="BK59:BQ59"/>
     <mergeCell ref="BK46:BQ46"/>
@@ -18660,6 +19961,7 @@
     <mergeCell ref="BE68:BG68"/>
     <mergeCell ref="AP43:AR43"/>
     <mergeCell ref="AM53:AO53"/>
+    <mergeCell ref="BE74:BG74"/>
     <mergeCell ref="AM47:AO47"/>
     <mergeCell ref="B10:D11"/>
     <mergeCell ref="J45:P45"/>
@@ -18673,10 +19975,14 @@
     <mergeCell ref="AV71:AX71"/>
     <mergeCell ref="E53:I53"/>
     <mergeCell ref="AE70:AF70"/>
+    <mergeCell ref="AY72:BA72"/>
     <mergeCell ref="AM48:AO48"/>
+    <mergeCell ref="BB73:BD73"/>
+    <mergeCell ref="Q74:W74"/>
     <mergeCell ref="Q49:W49"/>
     <mergeCell ref="E68:I68"/>
     <mergeCell ref="BK43:BQ43"/>
+    <mergeCell ref="AV73:AX73"/>
     <mergeCell ref="AF6:AH6"/>
     <mergeCell ref="E55:I55"/>
     <mergeCell ref="AE32:AF32"/>
@@ -18696,6 +20002,8 @@
     <mergeCell ref="AY59:BA59"/>
     <mergeCell ref="AS70:AU70"/>
     <mergeCell ref="J71:P71"/>
+    <mergeCell ref="X72:AD72"/>
+    <mergeCell ref="AM73:AO73"/>
     <mergeCell ref="J58:P58"/>
     <mergeCell ref="AS32:AU32"/>
     <mergeCell ref="AM45:AO45"/>
@@ -18707,6 +20015,7 @@
     <mergeCell ref="BE23:BG23"/>
     <mergeCell ref="AJ36:AL36"/>
     <mergeCell ref="BK36:BQ36"/>
+    <mergeCell ref="J73:P73"/>
     <mergeCell ref="AS47:AU47"/>
     <mergeCell ref="AY54:BA54"/>
     <mergeCell ref="AJ29:AL29"/>
@@ -18724,6 +20033,7 @@
     <mergeCell ref="AV66:AX66"/>
     <mergeCell ref="X19:AD19"/>
     <mergeCell ref="AE60:AF60"/>
+    <mergeCell ref="B72:D72"/>
     <mergeCell ref="AS58:AU58"/>
     <mergeCell ref="AG34:AI34"/>
     <mergeCell ref="AV59:AX59"/>
@@ -18781,7 +20091,9 @@
     <mergeCell ref="X13:AD13"/>
     <mergeCell ref="AS15:AU15"/>
     <mergeCell ref="AE48:AF48"/>
+    <mergeCell ref="AP75:AR75"/>
     <mergeCell ref="BH27:BJ27"/>
+    <mergeCell ref="BK75:BQ75"/>
     <mergeCell ref="AS55:AU55"/>
     <mergeCell ref="BE37:BG37"/>
     <mergeCell ref="AJ50:AL50"/>
@@ -18794,11 +20106,14 @@
     <mergeCell ref="BB28:BD28"/>
     <mergeCell ref="AG41:AI41"/>
     <mergeCell ref="BH69:BJ69"/>
+    <mergeCell ref="AS73:AU73"/>
+    <mergeCell ref="E72:I72"/>
     <mergeCell ref="BH35:BJ35"/>
     <mergeCell ref="AP39:AR39"/>
     <mergeCell ref="AP14:AR14"/>
     <mergeCell ref="BH22:BJ22"/>
     <mergeCell ref="AG56:AI56"/>
+    <mergeCell ref="X73:AD73"/>
     <mergeCell ref="AJ39:AL39"/>
     <mergeCell ref="J16:P16"/>
     <mergeCell ref="BK39:BQ39"/>
@@ -18850,6 +20165,7 @@
     <mergeCell ref="AV16:AX16"/>
     <mergeCell ref="Q63:W63"/>
     <mergeCell ref="Q50:W50"/>
+    <mergeCell ref="AM72:AO72"/>
     <mergeCell ref="AJ27:AL27"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="AY41:BA41"/>
@@ -18879,6 +20195,7 @@
     <mergeCell ref="AP15:AR15"/>
     <mergeCell ref="AS16:AU16"/>
     <mergeCell ref="AM54:AO54"/>
+    <mergeCell ref="BH72:BJ72"/>
     <mergeCell ref="AV10:BJ10"/>
     <mergeCell ref="BE27:BG27"/>
     <mergeCell ref="J17:P17"/>
@@ -18921,7 +20238,9 @@
     <mergeCell ref="AS69:AU69"/>
     <mergeCell ref="BH56:BJ56"/>
     <mergeCell ref="X29:AD29"/>
+    <mergeCell ref="AJ73:AL73"/>
     <mergeCell ref="AP35:AR35"/>
+    <mergeCell ref="BK73:BQ73"/>
     <mergeCell ref="BH31:BJ31"/>
     <mergeCell ref="AJ48:AL48"/>
     <mergeCell ref="AV42:AX42"/>
@@ -18931,8 +20250,10 @@
     <mergeCell ref="AJ66:AL66"/>
     <mergeCell ref="BE46:BG46"/>
     <mergeCell ref="AG70:AI70"/>
+    <mergeCell ref="AE72:AF72"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
+    <mergeCell ref="AP74:AR74"/>
     <mergeCell ref="BK20:BQ20"/>
     <mergeCell ref="AY28:BA28"/>
     <mergeCell ref="B34:D34"/>
@@ -18953,6 +20274,7 @@
     <mergeCell ref="Q68:W68"/>
     <mergeCell ref="BK15:BQ15"/>
     <mergeCell ref="AE17:AF17"/>
+    <mergeCell ref="BE73:BG73"/>
     <mergeCell ref="E15:I15"/>
     <mergeCell ref="AV20:AX20"/>
     <mergeCell ref="BE48:BG48"/>
@@ -18981,6 +20303,7 @@
     <mergeCell ref="J20:P20"/>
     <mergeCell ref="AV47:AX47"/>
     <mergeCell ref="B43:D43"/>
+    <mergeCell ref="AY75:BA75"/>
     <mergeCell ref="BE51:BG51"/>
     <mergeCell ref="AY50:BA50"/>
     <mergeCell ref="BB55:BD55"/>
@@ -18989,6 +20312,7 @@
     <mergeCell ref="J22:P22"/>
     <mergeCell ref="BH62:BJ62"/>
     <mergeCell ref="AV38:AX38"/>
+    <mergeCell ref="X75:AD75"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="BK35:BQ35"/>
     <mergeCell ref="AY39:BA39"/>
@@ -19003,10 +20327,13 @@
     <mergeCell ref="BE67:BG67"/>
     <mergeCell ref="AG13:AI13"/>
     <mergeCell ref="AV33:AX33"/>
+    <mergeCell ref="AJ74:AL74"/>
     <mergeCell ref="AP36:AR36"/>
     <mergeCell ref="AS37:AU37"/>
     <mergeCell ref="AE14:AF14"/>
     <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="BK74:BQ74"/>
+    <mergeCell ref="AM75:AO75"/>
     <mergeCell ref="J38:P38"/>
     <mergeCell ref="K7:M7"/>
     <mergeCell ref="A3:E3"/>
@@ -19026,6 +20353,8 @@
     <mergeCell ref="AY21:BA21"/>
     <mergeCell ref="BB66:BD66"/>
     <mergeCell ref="Q67:W67"/>
+    <mergeCell ref="AG73:AI73"/>
+    <mergeCell ref="B75:D75"/>
     <mergeCell ref="AV35:AX35"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
@@ -19040,6 +20369,7 @@
     <mergeCell ref="X65:AD65"/>
     <mergeCell ref="AM66:AO66"/>
     <mergeCell ref="Q69:W69"/>
+    <mergeCell ref="BH75:BJ75"/>
     <mergeCell ref="AE27:AF27"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
@@ -19073,6 +20403,7 @@
     <mergeCell ref="B65:D65"/>
     <mergeCell ref="AJ64:AL64"/>
     <mergeCell ref="T7:V7"/>
+    <mergeCell ref="J72:P72"/>
     <mergeCell ref="J28:P28"/>
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="BK49:BQ49"/>
@@ -19102,6 +20433,7 @@
     <mergeCell ref="AM62:AO62"/>
     <mergeCell ref="AJ17:AL17"/>
     <mergeCell ref="AM56:AO56"/>
+    <mergeCell ref="BB74:BD74"/>
     <mergeCell ref="J54:P54"/>
     <mergeCell ref="AM43:AO43"/>
     <mergeCell ref="J41:P41"/>
@@ -19111,13 +20443,16 @@
     <mergeCell ref="AY71:BA71"/>
     <mergeCell ref="E62:I62"/>
     <mergeCell ref="J56:P56"/>
+    <mergeCell ref="BE72:BG72"/>
     <mergeCell ref="AY58:BA58"/>
     <mergeCell ref="AS71:AU71"/>
     <mergeCell ref="J43:P43"/>
     <mergeCell ref="X25:AD25"/>
     <mergeCell ref="BB69:BD69"/>
     <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="AV72:AX72"/>
     <mergeCell ref="E64:I64"/>
+    <mergeCell ref="AY73:BA73"/>
     <mergeCell ref="X71:AD71"/>
     <mergeCell ref="E51:I51"/>
     <mergeCell ref="BK31:BQ31"/>
@@ -19151,16 +20486,17 @@
     <mergeCell ref="AG31:AI31"/>
     <mergeCell ref="AV56:AX56"/>
     <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E75:I75"/>
     <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE17 AE19:AE25 AE27:AE29 AE31:AE39 AE41:AE43 AE45:AE51 AE53:AE56 AE58:AE60 AE62:AE71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE17 AE19:AE25 AE27:AE29 AE31:AE39 AE41:AE43 AE45:AE51 AE53:AE56 AE58:AE60 AE62:AE75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG17 AG19:AG25 AG27:AG29 AG31:AG39 AG41:AG43 AG45:AG51 AG53:AG56 AG58:AG60 AG62:AG71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG17 AG19:AG25 AG27:AG29 AG31:AG39 AG41:AG43 AG45:AG51 AG53:AG56 AG58:AG60 AG62:AG75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV17 AV19:AV25 AV27:AV29 AV31:AV39 AV41:AV43 AV45:AV51 AV53:AV56 AV58:AV60 AV62:AV71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV17 AV19:AV25 AV27:AV29 AV31:AV39 AV41:AV43 AV45:AV51 AV53:AV56 AV58:AV60 AV62:AV75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者Excelデータ取込画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者Excelデータ取込画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AH4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1427,26 +1427,86 @@
       <c r="AG3" s="10" t="n"/>
       <c r="AH3" s="11" t="n"/>
     </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="20" t="inlineStr">
+        <is>
+          <t>実装との差分是正：①テンプレート列数の記述を 48列 → 50列 へ統一（13箇所）。2026-08-03 の 48→46（適用日・中止日を画面入力へ移して撤去）と 2026-08-04 の 46→50（#56405 購読者層分類の従属4項目を追加）が本書へ未反映で、ケースごとに 48列・46列が混在していた。統合テスト `dokusya-import.integration.spec.ts` が 50 列を検証している。②カテゴリ10を新設し、集計表に載っていなかった 052〜055 と新規 056/057 をまとめた（集計 51 → 57）。③ケース追加：056 購読者層分類の従属4項目（#56405）、057 メール重複のJA横断判定（#56568）</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="11" t="n"/>
+      <c r="W4" s="19" t="inlineStr"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="11" t="n"/>
+      <c r="AC4" s="19" t="inlineStr"/>
+      <c r="AD4" s="10" t="n"/>
+      <c r="AE4" s="10" t="n"/>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="24">
+    <mergeCell ref="O3:V3"/>
+    <mergeCell ref="W1:AB1"/>
+    <mergeCell ref="W3:AB3"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="AC4:AH4"/>
+    <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="O1:V1"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC2:AH2"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="W4:AB4"/>
     <mergeCell ref="B1:E1"/>
-    <mergeCell ref="AC2:AH2"/>
-    <mergeCell ref="AC1:AH1"/>
-    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
-    <mergeCell ref="W1:AB1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="W3:AB3"/>
-    <mergeCell ref="O1:V1"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="AC3:AH3"/>
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="W2:AB2"/>
-    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6370,7 +6430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ75"/>
+  <dimension ref="A1:BQ78"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8598,7 +8658,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">48列すべてのチェックボックスが表示されていること、新規登録モードでは必須列（`tetsuzuki_shurui`／`kanri_shiten_id`／`dokusya_busu`／`tanka_id`／`yubin_no`／`todofuken_code`／`shikuchoson`／`chome_banchi`／`renrakusaki_1`／`hanbaiten_id`／`shiharai_hoho`／`dokusya_kaishi_date`）が無効（非活性）かつチェック済みであること
+            <t xml:space="preserve">50列すべてのチェックボックスが表示されていること、新規登録モードでは必須列（`tetsuzuki_shurui`／`kanri_shiten_id`／`dokusya_busu`／`tanka_id`／`yubin_no`／`todofuken_code`／`shikuchoson`／`chome_banchi`／`renrakusaki_1`／`hanbaiten_id`／`shiharai_hoho`／`dokusya_kaishi_date`）が無効（非活性）かつチェック済みであること
 </t>
           </r>
           <r>
@@ -8903,7 +8963,7 @@
       <c r="D21" s="11" t="n"/>
       <c r="E21" s="46" t="inlineStr">
         <is>
-          <t>取込列パネル — 48列チェックボックスの表示確認</t>
+          <t>取込列パネル — 50列チェックボックスの表示確認</t>
         </is>
       </c>
       <c r="F21" s="10" t="n"/>
@@ -8998,7 +9058,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">取込列パネルが表示されること、全48列のチェックボックスが表示されること
+            <t xml:space="preserve">取込列パネルが表示されること、全50列のチェックボックスが表示されること
 </t>
           </r>
           <r>
@@ -9049,7 +9109,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・列順序はテンプレートファイル（48列固定）と一致すること
+            <t xml:space="preserve">・列順序はテンプレートファイル（50列固定）と一致すること
 </t>
           </r>
           <r>
@@ -10674,7 +10734,7 @@
         <is>
           <t>・role: JA_HONTEN
 ・ログイン済 + MFA認証済
-・テストファイル：購読者3行を含む `.xlsx`、シート名「購読者」、48列ヘッダ</t>
+・テストファイル：購読者3行を含む `.xlsx`、シート名「購読者」、50列ヘッダ</t>
         </is>
       </c>
       <c r="K31" s="10" t="n"/>
@@ -11060,7 +11120,7 @@
       <c r="BP32" s="10" t="n"/>
       <c r="BQ32" s="11" t="n"/>
     </row>
-    <row r="33" ht="336" customHeight="1">
+    <row r="33" ht="352" customHeight="1">
       <c r="A33" s="44" t="n">
         <v>18</v>
       </c>
@@ -11109,7 +11169,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">プレビュー初期表示で全48列が表示されていることを確認
+            <t xml:space="preserve">プレビュー初期表示で全50列が表示されていることを確認
 </t>
           </r>
           <r>
@@ -11169,7 +11229,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">プレビューに48列分のヘッダと3行のデータが表示されること
+            <t xml:space="preserve">プレビューに50列分のヘッダと3行のデータが表示されること
 </t>
           </r>
           <r>
@@ -11203,7 +11263,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">プレビューからチェック解除された3列が非表示となり、46列分のヘッダとデータのみ表示されること
+            <t xml:space="preserve">プレビューからチェック解除された3列が非表示となり、残りの列分のヘッダとデータのみ表示されること（全50列のうちチェック解除分を除いた列数）
 </t>
           </r>
           <r>
@@ -12720,7 +12780,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">シート名が「購読者」であること、1行目に48列のヘッダーが含まれていること
+            <t xml:space="preserve">シート名が「購読者」であること、1行目に50列のヘッダーが含まれていること
 </t>
           </r>
           <r>
@@ -12737,7 +12797,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・列順は `screen-design.md §3.1` および `api.md §テンプレートファイル仕様` に従う（48列固定）</t>
+            <t>・列順は `screen-design.md §3.1` および `api.md §テンプレートファイル仕様` に従う（50列固定）</t>
           </r>
         </is>
       </c>
@@ -12804,7 +12864,7 @@
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="46" t="inlineStr">
         <is>
-          <t>テンプレート — 48列ヘッダーの順序・列数確認</t>
+          <t>テンプレート — 50列ヘッダーの順序・列数確認</t>
         </is>
       </c>
       <c r="F42" s="10" t="n"/>
@@ -12857,7 +12917,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>48列分のヘッダー文字列と列数を確認</t>
+            <t>50列分のヘッダー文字列と列数を確認</t>
           </r>
         </is>
       </c>
@@ -12883,7 +12943,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">シート「購読者」の1行目に48列のヘッダーが表示されていること
+            <t xml:space="preserve">シート「購読者」の1行目に50列のヘッダーが表示されていること
 </t>
           </r>
           <r>
@@ -12900,7 +12960,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">ヘッダーが `screen-design.md §画面項目定義` および `api.md §テンプレートファイル仕様` の定義順で並んでいること、列数がちょうど48列であること
+            <t xml:space="preserve">ヘッダーが `screen-design.md §画面項目定義` および `api.md §テンプレートファイル仕様` の定義順で並んでいること、列数がちょうど50列であること
 </t>
           </r>
           <r>
@@ -18208,322 +18268,74 @@
       <c r="BP71" s="10" t="n"/>
       <c r="BQ71" s="11" t="n"/>
     </row>
-    <row r="72" ht="450" customHeight="1">
-      <c r="A72" s="44" t="n">
-        <v>52</v>
-      </c>
-      <c r="B72" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-016-052</t>
-        </is>
-      </c>
+    <row r="72" ht="22.5" customHeight="1">
+      <c r="A72" s="32" t="inlineStr">
+        <is>
+          <t>業務ロジック — 適用日／一括中止・取込列の拡張（Function — Dates / Bulk-stop / Columns）</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="n"/>
       <c r="C72" s="10" t="n"/>
-      <c r="D72" s="11" t="n"/>
-      <c r="E72" s="46" t="inlineStr">
-        <is>
-          <t>適用日／中止日 — 画面入力・相互排他・モード別の可否</t>
-        </is>
-      </c>
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="10" t="n"/>
       <c r="F72" s="10" t="n"/>
       <c r="G72" s="10" t="n"/>
       <c r="H72" s="10" t="n"/>
-      <c r="I72" s="11" t="n"/>
-      <c r="J72" s="46" t="inlineStr">
-        <is>
-          <t>・role: JA_HONTEN（`dokusya.import` 保有）
-・テンプレートをダウンロード済み（46列）</t>
-        </is>
-      </c>
+      <c r="I72" s="10" t="n"/>
+      <c r="J72" s="10" t="n"/>
       <c r="K72" s="10" t="n"/>
       <c r="L72" s="10" t="n"/>
       <c r="M72" s="10" t="n"/>
       <c r="N72" s="10" t="n"/>
       <c r="O72" s="10" t="n"/>
-      <c r="P72" s="11" t="n"/>
-      <c r="Q72" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">テンプレートのヘッダー行を確認する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">取込モード＝新規登録 の状態で「読者情報変更適用日」「購読中止日」の入力欄を確認する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">取込モード＝更新 に切り替え、読者情報変更適用日に未来日を入力する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">続けて購読中止日に日付を入力しようとする
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ5：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">読者情報変更適用日を空にしてから購読中止日に日付を入力する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ6：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>更新モードで両方とも空のまま「取込開始」をクリックする</t>
-          </r>
-        </is>
-      </c>
+      <c r="P72" s="10" t="n"/>
+      <c r="Q72" s="10" t="n"/>
       <c r="R72" s="10" t="n"/>
       <c r="S72" s="10" t="n"/>
       <c r="T72" s="10" t="n"/>
       <c r="U72" s="10" t="n"/>
       <c r="V72" s="10" t="n"/>
-      <c r="W72" s="11" t="n"/>
-      <c r="X72" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">「読者情報変更適用日」「購読中止日」の列が**存在しないこと**（46列。購読種別も無い）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">両方の入力欄が非活性であること（新規登録に変更適用日・中止日の概念が無い）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">入力できること。購読中止日の入力欄が非活性になること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">購読中止日が入力できないこと（相互排他）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ5：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">購読中止日が入力でき、読者情報変更適用日が非活性になること。ACSMS-MSG-016-014 が表示されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ6：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ACSMS-MSG-016-008 が表示され、APIが呼ばれないこと
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・DevTools で両方を同時に送った場合は 400（`VALIDATION_ERROR` / ACSMS-MSG-016-007）が返ること。画面の抑止は境界ではなくBEでも弾く
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・新規登録でどちらかを送った場合は 400（ACSMS-MSG-016-009 / ACSMS-MSG-016-010）</t>
-          </r>
-        </is>
-      </c>
+      <c r="W72" s="10" t="n"/>
+      <c r="X72" s="10" t="n"/>
       <c r="Y72" s="10" t="n"/>
       <c r="Z72" s="10" t="n"/>
       <c r="AA72" s="10" t="n"/>
       <c r="AB72" s="10" t="n"/>
       <c r="AC72" s="10" t="n"/>
-      <c r="AD72" s="11" t="n"/>
-      <c r="AE72" s="45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF72" s="11" t="n"/>
-      <c r="AG72" s="45" t="inlineStr"/>
+      <c r="AD72" s="10" t="n"/>
+      <c r="AE72" s="10" t="n"/>
+      <c r="AF72" s="10" t="n"/>
+      <c r="AG72" s="10" t="n"/>
       <c r="AH72" s="10" t="n"/>
-      <c r="AI72" s="11" t="n"/>
-      <c r="AJ72" s="45" t="inlineStr"/>
+      <c r="AI72" s="10" t="n"/>
+      <c r="AJ72" s="10" t="n"/>
       <c r="AK72" s="10" t="n"/>
-      <c r="AL72" s="11" t="n"/>
-      <c r="AM72" s="45" t="inlineStr"/>
+      <c r="AL72" s="10" t="n"/>
+      <c r="AM72" s="10" t="n"/>
       <c r="AN72" s="10" t="n"/>
-      <c r="AO72" s="11" t="n"/>
-      <c r="AP72" s="45" t="inlineStr"/>
+      <c r="AO72" s="10" t="n"/>
+      <c r="AP72" s="10" t="n"/>
       <c r="AQ72" s="10" t="n"/>
-      <c r="AR72" s="11" t="n"/>
-      <c r="AS72" s="45" t="inlineStr"/>
+      <c r="AR72" s="10" t="n"/>
+      <c r="AS72" s="10" t="n"/>
       <c r="AT72" s="10" t="n"/>
-      <c r="AU72" s="11" t="n"/>
-      <c r="AV72" s="45" t="inlineStr"/>
+      <c r="AU72" s="10" t="n"/>
+      <c r="AV72" s="10" t="n"/>
       <c r="AW72" s="10" t="n"/>
-      <c r="AX72" s="11" t="n"/>
-      <c r="AY72" s="45" t="inlineStr"/>
+      <c r="AX72" s="10" t="n"/>
+      <c r="AY72" s="10" t="n"/>
       <c r="AZ72" s="10" t="n"/>
-      <c r="BA72" s="11" t="n"/>
-      <c r="BB72" s="45" t="inlineStr"/>
+      <c r="BA72" s="10" t="n"/>
+      <c r="BB72" s="10" t="n"/>
       <c r="BC72" s="10" t="n"/>
-      <c r="BD72" s="11" t="n"/>
-      <c r="BE72" s="45" t="inlineStr"/>
+      <c r="BD72" s="10" t="n"/>
+      <c r="BE72" s="10" t="n"/>
       <c r="BF72" s="10" t="n"/>
-      <c r="BG72" s="11" t="n"/>
-      <c r="BH72" s="45" t="inlineStr"/>
+      <c r="BG72" s="10" t="n"/>
+      <c r="BH72" s="10" t="n"/>
       <c r="BI72" s="10" t="n"/>
-      <c r="BJ72" s="11" t="n"/>
-      <c r="BK72" s="46" t="inlineStr"/>
+      <c r="BJ72" s="10" t="n"/>
+      <c r="BK72" s="10" t="n"/>
       <c r="BL72" s="10" t="n"/>
       <c r="BM72" s="10" t="n"/>
       <c r="BN72" s="10" t="n"/>
@@ -18533,18 +18345,18 @@
     </row>
     <row r="73" ht="450" customHeight="1">
       <c r="A73" s="44" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B73" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-016-053</t>
+          <t>ACSMS-TC-016-052</t>
         </is>
       </c>
       <c r="C73" s="10" t="n"/>
       <c r="D73" s="11" t="n"/>
       <c r="E73" s="46" t="inlineStr">
         <is>
-          <t>更新 — 購読種別ごとの適用日ルールと帳票影響項目のロック</t>
+          <t>適用日／中止日 — 画面入力・相互排他・モード別の可否</t>
         </is>
       </c>
       <c r="F73" s="10" t="n"/>
@@ -18553,8 +18365,8 @@
       <c r="I73" s="11" t="n"/>
       <c r="J73" s="46" t="inlineStr">
         <is>
-          <t>・role: JA_HONTEN
-・事前データ：紙版・電子版の既存購読者（購読開始日は過去日）</t>
+          <t>・role: JA_HONTEN（`dokusya.import` 保有）
+・テンプレートをダウンロード済み（50列）</t>
         </is>
       </c>
       <c r="K73" s="10" t="n"/>
@@ -18579,7 +18391,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">更新モード × 電子版 を選び、読者情報変更適用日の入力欄を確認する
+            <t xml:space="preserve">テンプレートのヘッダー行を確認する
 </t>
           </r>
           <r>
@@ -18596,7 +18408,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">更新モード × 紙版 に切り替え、読者情報変更適用日に**当日**を入力する
+            <t xml:space="preserve">取込モード＝新規登録 の状態で「読者情報変更適用日」「購読中止日」の入力欄を確認する
 </t>
           </r>
           <r>
@@ -18613,7 +18425,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">取込列パネルで 購読部数 / 販売店コード / 郵便番号 のチェックボックスを確認する
+            <t xml:space="preserve">取込モード＝更新 に切り替え、読者情報変更適用日に未来日を入力する
 </t>
           </r>
           <r>
@@ -18630,7 +18442,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">読者情報変更適用日を**未来日**に変更する
+            <t xml:space="preserve">続けて購読中止日に日付を入力しようとする
 </t>
           </r>
           <r>
@@ -18647,7 +18459,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>当日を指定したまま DevTools で `selected_columns` に `hanbaiten_code` を含めて送信する</t>
+            <t xml:space="preserve">読者情報変更適用日を空にしてから購読中止日に日付を入力する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>更新モードで両方とも空のまま「取込開始」をクリックする</t>
           </r>
         </is>
       </c>
@@ -18673,7 +18502,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">入力欄に当日が表示され、非活性であること。ACSMS-MSG-016-012 が表示されること
+            <t xml:space="preserve">「読者情報変更適用日」「購読中止日」の列が**存在しないこと**（50列。購読種別も無い）
 </t>
           </r>
           <r>
@@ -18690,7 +18519,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">入力できること
+            <t xml:space="preserve">両方の入力欄が非活性であること（新規登録に変更適用日・中止日の概念が無い）
 </t>
           </r>
           <r>
@@ -18707,7 +18536,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">帳票影響項目12列（購読部数・販売店コード・購読者住所4項目・配達先住所5項目）が選択できないこと。ACSMS-MSG-016-013 が表示されること。備考など帳票に影響しない列は選択できること
+            <t xml:space="preserve">入力できること。購読中止日の入力欄が非活性になること
 </t>
           </r>
           <r>
@@ -18724,7 +18553,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">帳票影響項目が選択可能に戻ること（＝予約変更）
+            <t xml:space="preserve">購読中止日が入力できないこと（相互排他）
 </t>
           </r>
           <r>
@@ -18741,7 +18570,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">400（`IMPORT_VALIDATION_ERROR`）が返り、`errors[].field` が **`hanbaiten_code`**（`hanbaiten_id` ではない）であること
+            <t xml:space="preserve">購読中止日が入力でき、読者情報変更適用日が非活性になること。ACSMS-MSG-016-014 が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ACSMS-MSG-016-008 が表示され、APIが呼ばれないこと
 </t>
           </r>
           <r>
@@ -18758,15 +18604,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・ステップ5は「当日変更で販売店は変えられない」ルールが Excel 経路からすり抜けていた不具合の回帰確認。取込行は販売店をコードで持つため、単票 dto の `hanbaiten_id` のままでは変更が検出されなかった
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・選択した帳票影響項目の値が既存と同じ場合は「変更なし」として 200 になること（既存値ロード漏れの回帰確認）</t>
+            <t xml:space="preserve">・DevTools で両方を同時に送った場合は 400（`VALIDATION_ERROR` / ACSMS-MSG-016-007）が返ること。画面の抑止は境界ではなくBEでも弾く
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・新規登録でどちらかを送った場合は 400（ACSMS-MSG-016-009 / ACSMS-MSG-016-010）</t>
           </r>
         </is>
       </c>
@@ -18822,18 +18668,18 @@
     </row>
     <row r="74" ht="450" customHeight="1">
       <c r="A74" s="44" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B74" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-016-054</t>
+          <t>ACSMS-TC-016-053</t>
         </is>
       </c>
       <c r="C74" s="10" t="n"/>
       <c r="D74" s="11" t="n"/>
       <c r="E74" s="46" t="inlineStr">
         <is>
-          <t>一括中止 — 解約予約の作成（紙版・連携なし）</t>
+          <t>更新 — 購読種別ごとの適用日ルールと帳票影響項目のロック</t>
         </is>
       </c>
       <c r="F74" s="10" t="n"/>
@@ -18843,7 +18689,7 @@
       <c r="J74" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN
-・事前データ：紙版の既存購読者（購読中・購読部数=3）</t>
+・事前データ：紙版・電子版の既存購読者（購読開始日は過去日）</t>
         </is>
       </c>
       <c r="K74" s="10" t="n"/>
@@ -18868,7 +18714,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">更新モードで購読中止日に未来日を入力する
+            <t xml:space="preserve">更新モード × 電子版 を選び、読者情報変更適用日の入力欄を確認する
 </t>
           </r>
           <r>
@@ -18885,7 +18731,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">取込列パネルを確認する
+            <t xml:space="preserve">更新モード × 紙版 に切り替え、読者情報変更適用日に**当日**を入力する
 </t>
           </r>
           <r>
@@ -18902,7 +18748,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">「取込開始」→ 確認ダイアログで「はい」
+            <t xml:space="preserve">取込列パネルで 購読部数 / 販売店コード / 郵便番号 のチェックボックスを確認する
 </t>
           </r>
           <r>
@@ -18919,7 +18765,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DB 確認: `SELECT dokusya_busu, dokusya_chushi_date, kaiyaku_flg, torikeshi_flg FROM t_dokusya_rireki WHERE dokusya_id = :id ORDER BY rireki_no DESC LIMIT 1`
+            <t xml:space="preserve">読者情報変更適用日を**未来日**に変更する
 </t>
           </r>
           <r>
@@ -18936,24 +18782,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DB 確認: `SELECT dokusya_chushi_date, tetsuzuki_shurui, dokusya_busu FROM t_dokusya WHERE dokusya_id = :id`
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ6：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>一覧（SCR-014）で該当行の「購読中止日」列を確認する</t>
+            <t>当日を指定したまま DevTools で `selected_columns` に `hanbaiten_code` を含めて送信する</t>
           </r>
         </is>
       </c>
@@ -18979,7 +18808,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">入力でき、ACSMS-MSG-016-014 が表示されること
+            <t xml:space="preserve">入力欄に当日が表示され、非活性であること。ACSMS-MSG-016-012 が表示されること
 </t>
           </r>
           <r>
@@ -18996,7 +18825,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">チェックボックスがID列だけに縮退していること
+            <t xml:space="preserve">入力できること
 </t>
           </r>
           <r>
@@ -19013,7 +18842,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">ACSMS-MSG-016-004 が表示されること
+            <t xml:space="preserve">帳票影響項目12列（購読部数・販売店コード・購読者住所4項目・配達先住所5項目）が選択できないこと。ACSMS-MSG-016-013 が表示されること。備考など帳票に影響しない列は選択できること
 </t>
           </r>
           <r>
@@ -19030,7 +18859,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">`dokusya_busu=0`・`dokusya_chushi_date=入力日`・`kaiyaku_flg=false`・`torikeshi_flg=false` の予約行が1件追加されていること
+            <t xml:space="preserve">帳票影響項目が選択可能に戻ること（＝予約変更）
 </t>
           </r>
           <r>
@@ -19047,24 +18876,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">`dokusya_chushi_date` が入力日で反映されていること。`tetsuzuki_shurui=1`（購読中のまま＝確定は到来日バッチ）、`dokusya_busu` は元の3のまま（予約は master の部数を変えない）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ6：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">入力した中止日が表示されていること
+            <t xml:space="preserve">400（`IMPORT_VALIDATION_ERROR`）が返り、`errors[].field` が **`hanbaiten_code`**（`hanbaiten_id` ではない）であること
 </t>
           </r>
           <r>
@@ -19081,15 +18893,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・`selected_columns` に他の列を含めて DevTools から送っても、それらの列は更新されないこと（一括中止はキー列のみ）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・紙版は電子版システムへの連携を行わないこと</t>
+            <t xml:space="preserve">・ステップ5は「当日変更で販売店は変えられない」ルールが Excel 経路からすり抜けていた不具合の回帰確認。取込行は販売店をコードで持つため、単票 dto の `hanbaiten_id` のままでは変更が検出されなかった
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・選択した帳票影響項目の値が既存と同じ場合は「変更なし」として 200 になること（既存値ロード漏れの回帰確認）</t>
           </r>
         </is>
       </c>
@@ -19145,18 +18957,18 @@
     </row>
     <row r="75" ht="450" customHeight="1">
       <c r="A75" s="44" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B75" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-016-055</t>
+          <t>ACSMS-TC-016-054</t>
         </is>
       </c>
       <c r="C75" s="10" t="n"/>
       <c r="D75" s="11" t="n"/>
       <c r="E75" s="46" t="inlineStr">
         <is>
-          <t>一括中止 — 電子版の連携失敗で全ロールバック＋打ち消し</t>
+          <t>一括中止 — 解約予約の作成（紙版・連携なし）</t>
         </is>
       </c>
       <c r="F75" s="10" t="n"/>
@@ -19166,9 +18978,7 @@
       <c r="J75" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN
-・事前データ：電子版の既存購読者3件（電子版会員IDあり・非クレカ）
-・電子版連携が有効（DENSHIBAN_PUSH_ENABLED=true）
-・3件目の連携がエラーを返すよう擬似環境を設定</t>
+・事前データ：紙版の既存購読者（購読中・購読部数=3）</t>
         </is>
       </c>
       <c r="K75" s="10" t="n"/>
@@ -19193,7 +19003,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">更新モードで購読中止日に未来日を入力し、3件を取込む
+            <t xml:space="preserve">更新モードで購読中止日に未来日を入力する
 </t>
           </r>
           <r>
@@ -19210,7 +19020,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DB 確認: `SELECT COUNT(*) FROM t_dokusya_rireki WHERE dokusya_id IN (:ids) AND dokusya_chushi_date IS NOT NULL`
+            <t xml:space="preserve">取込列パネルを確認する
 </t>
           </r>
           <r>
@@ -19227,7 +19037,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">DB 確認: `SELECT dokusya_chushi_date FROM t_dokusya WHERE dokusya_id IN (:ids)`
+            <t xml:space="preserve">「取込開始」→ 確認ダイアログで「はい」
 </t>
           </r>
           <r>
@@ -19244,7 +19054,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">電子版連携ログを確認する
+            <t xml:space="preserve">DB 確認: `SELECT dokusya_busu, dokusya_chushi_date, kaiyaku_flg, torikeshi_flg FROM t_dokusya_rireki WHERE dokusya_id = :id ORDER BY rireki_no DESC LIMIT 1`
 </t>
           </r>
           <r>
@@ -19261,7 +19071,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">`t_log` を確認する（`log_type=3`）
+            <t xml:space="preserve">DB 確認: `SELECT dokusya_chushi_date, tetsuzuki_shurui, dokusya_busu FROM t_dokusya WHERE dokusya_id = :id`
 </t>
           </r>
           <r>
@@ -19278,7 +19088,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>501件の電子版一括中止を試行する</t>
+            <t>一覧（SCR-014）で該当行の「購読中止日」列を確認する</t>
           </r>
         </is>
       </c>
@@ -19304,7 +19114,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">エラーが表示され、取込が失敗すること（電子版が返した理由が表示されること）
+            <t xml:space="preserve">入力でき、ACSMS-MSG-016-014 が表示されること
 </t>
           </r>
           <r>
@@ -19321,7 +19131,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">予約行が**1件も作成されていないこと**（全件ロールバック）
+            <t xml:space="preserve">チェックボックスがID列だけに縮退していること
 </t>
           </r>
           <r>
@@ -19338,7 +19148,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">`dokusya_chushi_date` が更新されていないこと
+            <t xml:space="preserve">ACSMS-MSG-016-004 が表示されること
 </t>
           </r>
           <r>
@@ -19355,7 +19165,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">1件目・2件目に `action_kbn=cancel` + `cancel_ym=YYYYMM` が送られた後、**同じ2件へ打ち消し（`cancel_ym` 空文字）が送られていること**
+            <t xml:space="preserve">`dokusya_busu=0`・`dokusya_chushi_date=入力日`・`kaiyaku_flg=false`・`torikeshi_flg=false` の予約行が1件追加されていること
 </t>
           </r>
           <r>
@@ -19372,7 +19182,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">エラーログが記録されていること。打ち消しにも失敗した場合は、対象の電子版会員IDがメッセージに含まれていること（運用の手動対応用）
+            <t xml:space="preserve">`dokusya_chushi_date` が入力日で反映されていること。`tetsuzuki_shurui=1`（購読中のまま＝確定は到来日バッチ）、`dokusya_busu` は元の3のまま（予約は master の部数を変えない）
 </t>
           </r>
           <r>
@@ -19389,7 +19199,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">400（`VALIDATION_ERROR` / ACSMS-MSG-016-011）が返り、1件も処理されないこと
+            <t xml:space="preserve">入力した中止日が表示されていること
 </t>
           </r>
           <r>
@@ -19406,23 +19216,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・打ち消しは電子版APIに解約取消の処理区分が無いため `cancel` + 空 `cancel_ym` で行う（顧客判断 2026-08）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・**空 `cancel_ym` を電子版が受理するかは未検証**。拒否される場合、この打ち消しも SCR-014 の予約取消も成立しないため、統合テストではこの項目を最優先で確認すること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・紙版は連携が無いため本ケースの対象外（通常の全件ロールバックのみ）</t>
+            <t xml:space="preserve">・`selected_columns` に他の列を含めて DevTools から送っても、それらの列は更新されないこと（一括中止はキー列のみ）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・紙版は電子版システムへの連携を行わないこと</t>
           </r>
         </is>
       </c>
@@ -19434,7 +19236,7 @@
       <c r="AD75" s="11" t="n"/>
       <c r="AE75" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF75" s="11" t="n"/>
@@ -19476,8 +19278,1098 @@
       <c r="BP75" s="10" t="n"/>
       <c r="BQ75" s="11" t="n"/>
     </row>
+    <row r="76" ht="450" customHeight="1">
+      <c r="A76" s="44" t="n">
+        <v>55</v>
+      </c>
+      <c r="B76" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-016-055</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="11" t="n"/>
+      <c r="E76" s="46" t="inlineStr">
+        <is>
+          <t>一括中止 — 電子版の連携失敗で全ロールバック＋打ち消し</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="10" t="n"/>
+      <c r="I76" s="11" t="n"/>
+      <c r="J76" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・事前データ：電子版の既存購読者3件（電子版会員IDあり・非クレカ）
+・電子版連携が有効（DENSHIBAN_PUSH_ENABLED=true）
+・3件目の連携がエラーを返すよう擬似環境を設定</t>
+        </is>
+      </c>
+      <c r="K76" s="10" t="n"/>
+      <c r="L76" s="10" t="n"/>
+      <c r="M76" s="10" t="n"/>
+      <c r="N76" s="10" t="n"/>
+      <c r="O76" s="10" t="n"/>
+      <c r="P76" s="11" t="n"/>
+      <c r="Q76" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">更新モードで購読中止日に未来日を入力し、3件を取込む
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DB 確認: `SELECT COUNT(*) FROM t_dokusya_rireki WHERE dokusya_id IN (:ids) AND dokusya_chushi_date IS NOT NULL`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DB 確認: `SELECT dokusya_chushi_date FROM t_dokusya WHERE dokusya_id IN (:ids)`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">電子版連携ログを確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`t_log` を確認する（`log_type=3`）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>501件の電子版一括中止を試行する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R76" s="10" t="n"/>
+      <c r="S76" s="10" t="n"/>
+      <c r="T76" s="10" t="n"/>
+      <c r="U76" s="10" t="n"/>
+      <c r="V76" s="10" t="n"/>
+      <c r="W76" s="11" t="n"/>
+      <c r="X76" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">エラーが表示され、取込が失敗すること（電子版が返した理由が表示されること）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">予約行が**1件も作成されていないこと**（全件ロールバック）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`dokusya_chushi_date` が更新されていないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">1件目・2件目に `action_kbn=cancel` + `cancel_ym=YYYYMM` が送られた後、**同じ2件へ打ち消し（`cancel_ym` 空文字）が送られていること**
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">エラーログが記録されていること。打ち消しにも失敗した場合は、対象の電子版会員IDがメッセージに含まれていること（運用の手動対応用）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">400（`VALIDATION_ERROR` / ACSMS-MSG-016-011）が返り、1件も処理されないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・打ち消しは電子版APIに解約取消の処理区分が無いため `cancel` + 空 `cancel_ym` で行う（顧客判断 2026-08）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・**空 `cancel_ym` を電子版が受理するかは未検証**。拒否される場合、この打ち消しも SCR-014 の予約取消も成立しないため、統合テストではこの項目を最優先で確認すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・紙版は連携が無いため本ケースの対象外（通常の全件ロールバックのみ）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y76" s="10" t="n"/>
+      <c r="Z76" s="10" t="n"/>
+      <c r="AA76" s="10" t="n"/>
+      <c r="AB76" s="10" t="n"/>
+      <c r="AC76" s="10" t="n"/>
+      <c r="AD76" s="11" t="n"/>
+      <c r="AE76" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF76" s="11" t="n"/>
+      <c r="AG76" s="45" t="inlineStr"/>
+      <c r="AH76" s="10" t="n"/>
+      <c r="AI76" s="11" t="n"/>
+      <c r="AJ76" s="45" t="inlineStr"/>
+      <c r="AK76" s="10" t="n"/>
+      <c r="AL76" s="11" t="n"/>
+      <c r="AM76" s="45" t="inlineStr"/>
+      <c r="AN76" s="10" t="n"/>
+      <c r="AO76" s="11" t="n"/>
+      <c r="AP76" s="45" t="inlineStr"/>
+      <c r="AQ76" s="10" t="n"/>
+      <c r="AR76" s="11" t="n"/>
+      <c r="AS76" s="45" t="inlineStr"/>
+      <c r="AT76" s="10" t="n"/>
+      <c r="AU76" s="11" t="n"/>
+      <c r="AV76" s="45" t="inlineStr"/>
+      <c r="AW76" s="10" t="n"/>
+      <c r="AX76" s="11" t="n"/>
+      <c r="AY76" s="45" t="inlineStr"/>
+      <c r="AZ76" s="10" t="n"/>
+      <c r="BA76" s="11" t="n"/>
+      <c r="BB76" s="45" t="inlineStr"/>
+      <c r="BC76" s="10" t="n"/>
+      <c r="BD76" s="11" t="n"/>
+      <c r="BE76" s="45" t="inlineStr"/>
+      <c r="BF76" s="10" t="n"/>
+      <c r="BG76" s="11" t="n"/>
+      <c r="BH76" s="45" t="inlineStr"/>
+      <c r="BI76" s="10" t="n"/>
+      <c r="BJ76" s="11" t="n"/>
+      <c r="BK76" s="46" t="inlineStr"/>
+      <c r="BL76" s="10" t="n"/>
+      <c r="BM76" s="10" t="n"/>
+      <c r="BN76" s="10" t="n"/>
+      <c r="BO76" s="10" t="n"/>
+      <c r="BP76" s="10" t="n"/>
+      <c r="BQ76" s="11" t="n"/>
+    </row>
+    <row r="77" ht="450" customHeight="1">
+      <c r="A77" s="44" t="n">
+        <v>56</v>
+      </c>
+      <c r="B77" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-016-056</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="n"/>
+      <c r="D77" s="11" t="n"/>
+      <c r="E77" s="46" t="inlineStr">
+        <is>
+          <t>取込列 — 購読者層分類の従属4項目（#56405）</t>
+        </is>
+      </c>
+      <c r="F77" s="10" t="n"/>
+      <c r="G77" s="10" t="n"/>
+      <c r="H77" s="10" t="n"/>
+      <c r="I77" s="11" t="n"/>
+      <c r="J77" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100、`dokusya.import` 権限あり）
+・テンプレートを最新版でダウンロード済み</t>
+        </is>
+      </c>
+      <c r="K77" s="10" t="n"/>
+      <c r="L77" s="10" t="n"/>
+      <c r="M77" s="10" t="n"/>
+      <c r="N77" s="10" t="n"/>
+      <c r="O77" s="10" t="n"/>
+      <c r="P77" s="11" t="n"/>
+      <c r="Q77" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">テンプレートをダウンロードし、ヘッダの列数と並び順を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">NEW モードで以下の行を取り込む
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・購読者層分類=0（農業者）、かつJAグループ役職員=TRUE、主な生産物=「0,1」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・購読者層分類=2（企業・団体）、農業関係=1
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・購読者層分類=999（その他）、読者属性（その他の内容）=`自営業`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・農業者分類に999を含む行、主な生産物（その他の内容）=`きのこ`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DBで保存結果を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT dokusyaso_bunrui, ja_yakushokuin_flg, nogyo_kankei_flg,
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">nogyosya_bunrui, dokusyaso_bunrui_sonota, nogyosya_bunrui_sonota
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_dokusya WHERE dokusya_id IN (...);
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">NEW モードで**親の条件を満たさない**行を取り込む
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・購読者層分類=3（学生）なのに かつJAグループ役職員=TRUE
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・購読者層分類=0（農業者）なのに 読者属性（その他の内容）=`テスト`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">UPDATE_PARTIAL モードで**従属項目の列だけ**を選択し、親の列（購読者層分類）を選択せずに取り込む
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>UPDATE_PARTIAL モードで**親の列と従属項目の列を両方**選択し、親が従属項目を許さない組合せで取り込む</t>
+          </r>
+        </is>
+      </c>
+      <c r="R77" s="10" t="n"/>
+      <c r="S77" s="10" t="n"/>
+      <c r="T77" s="10" t="n"/>
+      <c r="U77" s="10" t="n"/>
+      <c r="V77" s="10" t="n"/>
+      <c r="W77" s="11" t="n"/>
+      <c r="X77" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ヘッダが 50 列であること（46 → 50）。従属4項目が**親の分類の直後**に並ぶこと（かつJAグループ役職員・農業関係・読者属性（その他の内容）は購読者層分類の直後、主な生産物（その他の内容）は農業者分類の直後）。サンプル行の長さがヘッダと一致すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">取込が成功すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`ja_yakushokuin_flg=true`・`nogyo_kankei_flg=true`・`dokusyaso_bunrui_sonota='自営業'`・`nogyosya_bunrui_sonota='きのこ'` が保存されていること。Excel の TRUE/FALSE・1/0 のいずれの表記も boolean へ変換されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">親の条件を満たさない値はサーバ側で落とされ、`ja_yakushokuin_flg=false`・`dokusyaso_bunrui_sonota=''` が保存されること（画面登録 SCR-011 と同じ `buildBunruiPayload` を通すため、Excel からは画面で作れない組合せを入れられない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">従属項目の値がそのまま保存されること（親の列が取込対象でない場合、既存値が維持されるため取込行だけでは矛盾を判定できない。判定できないケースは許容する仕様）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">親が許さない組合せは落とされること（親の列も同時に更新対象のときだけ判定する）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・フラグ2項目は BOOLEAN 列として扱う。DTO が `@IsBoolean` で受けるため、文字列のままだと 400 になる
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・ステップ5で矛盾した組合せが DB に残っても、電子版 push は保存値から profession を組み直したうえで条件付き項目を出し分けるため V26〜V30 で同期は壊れない。実害は「意味の無いフラグが残る」だけで、画面から開いて保存し直せば整う
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・列は列名で突合するため物理的な順序は動作に影響しないが、テンプレートを目視で埋める顧客にとって親子が離れていると対応が読めないため順序を規定している</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y77" s="10" t="n"/>
+      <c r="Z77" s="10" t="n"/>
+      <c r="AA77" s="10" t="n"/>
+      <c r="AB77" s="10" t="n"/>
+      <c r="AC77" s="10" t="n"/>
+      <c r="AD77" s="11" t="n"/>
+      <c r="AE77" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF77" s="11" t="n"/>
+      <c r="AG77" s="45" t="inlineStr"/>
+      <c r="AH77" s="10" t="n"/>
+      <c r="AI77" s="11" t="n"/>
+      <c r="AJ77" s="45" t="inlineStr"/>
+      <c r="AK77" s="10" t="n"/>
+      <c r="AL77" s="11" t="n"/>
+      <c r="AM77" s="45" t="inlineStr"/>
+      <c r="AN77" s="10" t="n"/>
+      <c r="AO77" s="11" t="n"/>
+      <c r="AP77" s="45" t="inlineStr"/>
+      <c r="AQ77" s="10" t="n"/>
+      <c r="AR77" s="11" t="n"/>
+      <c r="AS77" s="45" t="inlineStr"/>
+      <c r="AT77" s="10" t="n"/>
+      <c r="AU77" s="11" t="n"/>
+      <c r="AV77" s="45" t="inlineStr"/>
+      <c r="AW77" s="10" t="n"/>
+      <c r="AX77" s="11" t="n"/>
+      <c r="AY77" s="45" t="inlineStr"/>
+      <c r="AZ77" s="10" t="n"/>
+      <c r="BA77" s="11" t="n"/>
+      <c r="BB77" s="45" t="inlineStr"/>
+      <c r="BC77" s="10" t="n"/>
+      <c r="BD77" s="11" t="n"/>
+      <c r="BE77" s="45" t="inlineStr"/>
+      <c r="BF77" s="10" t="n"/>
+      <c r="BG77" s="11" t="n"/>
+      <c r="BH77" s="45" t="inlineStr"/>
+      <c r="BI77" s="10" t="n"/>
+      <c r="BJ77" s="11" t="n"/>
+      <c r="BK77" s="46" t="inlineStr"/>
+      <c r="BL77" s="10" t="n"/>
+      <c r="BM77" s="10" t="n"/>
+      <c r="BN77" s="10" t="n"/>
+      <c r="BO77" s="10" t="n"/>
+      <c r="BP77" s="10" t="n"/>
+      <c r="BQ77" s="11" t="n"/>
+    </row>
+    <row r="78" ht="450" customHeight="1">
+      <c r="A78" s="44" t="n">
+        <v>57</v>
+      </c>
+      <c r="B78" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-016-057</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="11" t="n"/>
+      <c r="E78" s="46" t="inlineStr">
+        <is>
+          <t>取込バリデーション — メールアドレス重複がJA横断であること（#56568）</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="10" t="n"/>
+      <c r="I78" s="11" t="n"/>
+      <c r="J78" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100、`dokusya.import` 権限あり）
+・**別のJA**（ja_id=200）に 購読種別=電子版・メールアドレス `dup@example.com` の購読者が存在
+・自JA（ja_id=100）に 購読種別=紙版・メールアドレス `paper@example.com` の購読者が存在
+・別のJA（ja_id=200）に 購読種別=電子版・メールアドレス `deleted@example.com` の**論理削除済み**購読者が存在</t>
+        </is>
+      </c>
+      <c r="K78" s="10" t="n"/>
+      <c r="L78" s="10" t="n"/>
+      <c r="M78" s="10" t="n"/>
+      <c r="N78" s="10" t="n"/>
+      <c r="O78" s="10" t="n"/>
+      <c r="P78" s="11" t="n"/>
+      <c r="Q78" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">NEW モードで 購読種別=電子版・メールアドレス `dup@example.com` の行を取り込む
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">NEW モードで 購読種別=電子版・メールアドレス `paper@example.com` の行を取り込む
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">NEW モードで 購読種別=電子版・メールアドレス `deleted@example.com` の行を取り込む
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">NEW モードで **同一ファイル内**に 購読種別=電子版・同じメールアドレス `batch@example.com` の行を 2 行入れて取り込む
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">NEW モードで 購読種別=紙版・メールアドレス `paper@example.com` の行を取り込む
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>UPDATE_PARTIAL モードで、メールアドレス列を**選択せず**に既存の電子版購読者を更新する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R78" s="10" t="n"/>
+      <c r="S78" s="10" t="n"/>
+      <c r="T78" s="10" t="n"/>
+      <c r="U78" s="10" t="n"/>
+      <c r="V78" s="10" t="n"/>
+      <c r="W78" s="11" t="n"/>
+      <c r="X78" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">当該行がエラーとなり、`{ row: &lt;行番号&gt;, field: "email", message: "このメールアドレスは既に登録されています。" }` が返ること。**他JAのレコードであっても重複と判定される**こと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">取込が成功すること（重複判定の対象は `dokusya_shubetsu IN (2,3)` のみ。紙版のメールとは衝突しない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">取込が成功すること（論理削除済みレコードは対象外。メールアドレスを再利用できる）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2 行目がエラーとなること（同一取込バッチ内の電子版・併読行同士の重複も検知する）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">取込が成功すること（紙版同士のメール重複は従来どおり許容）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">メール重複チェックが実行されず、既存メールが維持されたまま更新が成功すること（email 列が対象でない UPDATE は素通し）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・電子版ではメールアドレスが会員の同定キー（ログインID）のため JA を跨いで一意でなければならない（顧客要件 2026-08 / #56568）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・従来は `ja_id = :ja_id` 条件付きで自JA内しか見ておらず、別JAに同一メールの電子版読者を作成できてしまった
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・同じ判定は画面登録（SCR-011）にも適用される</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y78" s="10" t="n"/>
+      <c r="Z78" s="10" t="n"/>
+      <c r="AA78" s="10" t="n"/>
+      <c r="AB78" s="10" t="n"/>
+      <c r="AC78" s="10" t="n"/>
+      <c r="AD78" s="11" t="n"/>
+      <c r="AE78" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF78" s="11" t="n"/>
+      <c r="AG78" s="45" t="inlineStr"/>
+      <c r="AH78" s="10" t="n"/>
+      <c r="AI78" s="11" t="n"/>
+      <c r="AJ78" s="45" t="inlineStr"/>
+      <c r="AK78" s="10" t="n"/>
+      <c r="AL78" s="11" t="n"/>
+      <c r="AM78" s="45" t="inlineStr"/>
+      <c r="AN78" s="10" t="n"/>
+      <c r="AO78" s="11" t="n"/>
+      <c r="AP78" s="45" t="inlineStr"/>
+      <c r="AQ78" s="10" t="n"/>
+      <c r="AR78" s="11" t="n"/>
+      <c r="AS78" s="45" t="inlineStr"/>
+      <c r="AT78" s="10" t="n"/>
+      <c r="AU78" s="11" t="n"/>
+      <c r="AV78" s="45" t="inlineStr"/>
+      <c r="AW78" s="10" t="n"/>
+      <c r="AX78" s="11" t="n"/>
+      <c r="AY78" s="45" t="inlineStr"/>
+      <c r="AZ78" s="10" t="n"/>
+      <c r="BA78" s="11" t="n"/>
+      <c r="BB78" s="45" t="inlineStr"/>
+      <c r="BC78" s="10" t="n"/>
+      <c r="BD78" s="11" t="n"/>
+      <c r="BE78" s="45" t="inlineStr"/>
+      <c r="BF78" s="10" t="n"/>
+      <c r="BG78" s="11" t="n"/>
+      <c r="BH78" s="45" t="inlineStr"/>
+      <c r="BI78" s="10" t="n"/>
+      <c r="BJ78" s="11" t="n"/>
+      <c r="BK78" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL78" s="10" t="n"/>
+      <c r="BM78" s="10" t="n"/>
+      <c r="BN78" s="10" t="n"/>
+      <c r="BO78" s="10" t="n"/>
+      <c r="BP78" s="10" t="n"/>
+      <c r="BQ78" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="1010">
+  <mergeCells count="1045">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="B60:D60"/>
@@ -19511,6 +20403,7 @@
     <mergeCell ref="AM65:AO65"/>
     <mergeCell ref="AG24:AI24"/>
     <mergeCell ref="BH39:BJ39"/>
+    <mergeCell ref="BB77:BD77"/>
     <mergeCell ref="W2:AH2"/>
     <mergeCell ref="X10:AD11"/>
     <mergeCell ref="A26:BQ26"/>
@@ -19523,13 +20416,16 @@
     <mergeCell ref="AV75:AX75"/>
     <mergeCell ref="BK42:BQ42"/>
     <mergeCell ref="Q38:W38"/>
+    <mergeCell ref="Q76:W76"/>
     <mergeCell ref="AE34:AF34"/>
+    <mergeCell ref="AY76:BA76"/>
     <mergeCell ref="AJ51:AL51"/>
     <mergeCell ref="AP71:AR71"/>
     <mergeCell ref="BK47:BQ47"/>
     <mergeCell ref="E25:I25"/>
     <mergeCell ref="X74:AD74"/>
     <mergeCell ref="X68:AD68"/>
+    <mergeCell ref="AS76:AU76"/>
     <mergeCell ref="AE36:AF36"/>
     <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="Q15:W15"/>
@@ -19541,6 +20437,7 @@
     <mergeCell ref="AM34:AO34"/>
     <mergeCell ref="AJ38:AL38"/>
     <mergeCell ref="AP73:AR73"/>
+    <mergeCell ref="X76:AD76"/>
     <mergeCell ref="J75:P75"/>
     <mergeCell ref="BE35:BG35"/>
     <mergeCell ref="BK48:BQ48"/>
@@ -19553,6 +20450,7 @@
     <mergeCell ref="AE31:AF31"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="AG45:AI45"/>
+    <mergeCell ref="AM78:AO78"/>
     <mergeCell ref="AS67:AU67"/>
     <mergeCell ref="AY29:BA29"/>
     <mergeCell ref="E20:I20"/>
@@ -19569,11 +20467,14 @@
     <mergeCell ref="AY31:BA31"/>
     <mergeCell ref="AJ35:AL35"/>
     <mergeCell ref="BK37:BQ37"/>
+    <mergeCell ref="Q77:W77"/>
+    <mergeCell ref="E78:I78"/>
     <mergeCell ref="AM55:AO55"/>
     <mergeCell ref="BH34:BJ34"/>
     <mergeCell ref="X23:AD23"/>
     <mergeCell ref="BE38:BG38"/>
     <mergeCell ref="AE64:AF64"/>
+    <mergeCell ref="B76:D76"/>
     <mergeCell ref="AS62:AU62"/>
     <mergeCell ref="AV63:AX63"/>
     <mergeCell ref="AP66:AR66"/>
@@ -19589,7 +20490,6 @@
     <mergeCell ref="AS64:AU64"/>
     <mergeCell ref="BE15:BG15"/>
     <mergeCell ref="AP68:AR68"/>
-    <mergeCell ref="Q72:W72"/>
     <mergeCell ref="J65:P65"/>
     <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="BE33:BG33"/>
@@ -19605,7 +20505,6 @@
     <mergeCell ref="Q46:W46"/>
     <mergeCell ref="BH55:BJ55"/>
     <mergeCell ref="AM24:AO24"/>
-    <mergeCell ref="AJ72:AL72"/>
     <mergeCell ref="AG27:AI27"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="AM60:AO60"/>
@@ -19618,6 +20517,7 @@
     <mergeCell ref="AV13:AX13"/>
     <mergeCell ref="BH42:BJ42"/>
     <mergeCell ref="AS17:AU17"/>
+    <mergeCell ref="AV78:AX78"/>
     <mergeCell ref="AS11:AU11"/>
     <mergeCell ref="BH29:BJ29"/>
     <mergeCell ref="Q41:W41"/>
@@ -19626,6 +20526,7 @@
     <mergeCell ref="AS19:AU19"/>
     <mergeCell ref="Q56:W56"/>
     <mergeCell ref="AS75:AU75"/>
+    <mergeCell ref="X77:AD77"/>
     <mergeCell ref="Q43:W43"/>
     <mergeCell ref="J14:P14"/>
     <mergeCell ref="AE39:AF39"/>
@@ -19641,6 +20542,7 @@
     <mergeCell ref="BE34:BG34"/>
     <mergeCell ref="BE28:BG28"/>
     <mergeCell ref="AJ41:AL41"/>
+    <mergeCell ref="J78:P78"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="BK10:BQ11"/>
     <mergeCell ref="J53:P53"/>
@@ -19665,7 +20567,7 @@
     <mergeCell ref="BK68:BQ68"/>
     <mergeCell ref="A44:BQ44"/>
     <mergeCell ref="AY47:BA47"/>
-    <mergeCell ref="AS72:AU72"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="E21:I21"/>
     <mergeCell ref="BH50:BJ50"/>
     <mergeCell ref="Q36:W36"/>
@@ -19703,7 +20605,7 @@
     <mergeCell ref="BB48:BD48"/>
     <mergeCell ref="AG68:AI68"/>
     <mergeCell ref="AG43:AI43"/>
-    <mergeCell ref="AP72:AR72"/>
+    <mergeCell ref="AM76:AO76"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="E49:I49"/>
     <mergeCell ref="J68:P68"/>
@@ -19717,6 +20619,7 @@
     <mergeCell ref="AV65:AX65"/>
     <mergeCell ref="BH45:BJ45"/>
     <mergeCell ref="AS20:AU20"/>
+    <mergeCell ref="E76:I76"/>
     <mergeCell ref="AP24:AR24"/>
     <mergeCell ref="BH32:BJ32"/>
     <mergeCell ref="B27:D27"/>
@@ -19734,6 +20637,7 @@
     <mergeCell ref="BH46:BJ46"/>
     <mergeCell ref="BE50:BG50"/>
     <mergeCell ref="AP19:AR19"/>
+    <mergeCell ref="BH76:BJ76"/>
     <mergeCell ref="BE31:BG31"/>
     <mergeCell ref="J21:P21"/>
     <mergeCell ref="A1:E1"/>
@@ -19753,8 +20657,10 @@
     <mergeCell ref="AE33:AF33"/>
     <mergeCell ref="BB36:BD36"/>
     <mergeCell ref="AV74:AX74"/>
+    <mergeCell ref="AP77:AR77"/>
     <mergeCell ref="E31:I31"/>
     <mergeCell ref="AV36:AX36"/>
+    <mergeCell ref="BK77:BQ77"/>
     <mergeCell ref="T6:V6"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="AE73:AF73"/>
@@ -19767,12 +20673,11 @@
     <mergeCell ref="J34:P34"/>
     <mergeCell ref="AY37:BA37"/>
     <mergeCell ref="BE65:BG65"/>
-    <mergeCell ref="BK72:BQ72"/>
+    <mergeCell ref="J74:P74"/>
     <mergeCell ref="AS35:AU35"/>
     <mergeCell ref="J49:P49"/>
-    <mergeCell ref="J74:P74"/>
+    <mergeCell ref="AE74:AF74"/>
     <mergeCell ref="AE68:AF68"/>
-    <mergeCell ref="AE74:AF74"/>
     <mergeCell ref="J36:P36"/>
     <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
@@ -19781,6 +20686,7 @@
     <mergeCell ref="AJ70:AL70"/>
     <mergeCell ref="AV21:AX21"/>
     <mergeCell ref="AY53:BA53"/>
+    <mergeCell ref="AM77:AO77"/>
     <mergeCell ref="BK24:BQ24"/>
     <mergeCell ref="X45:AD45"/>
     <mergeCell ref="E50:I50"/>
@@ -19820,11 +20726,13 @@
     <mergeCell ref="AE23:AF23"/>
     <mergeCell ref="AC6:AE6"/>
     <mergeCell ref="AG39:AI39"/>
+    <mergeCell ref="BH77:BJ77"/>
     <mergeCell ref="BB17:BD17"/>
     <mergeCell ref="AV49:AX49"/>
     <mergeCell ref="BB11:BD11"/>
     <mergeCell ref="AJ25:AL25"/>
     <mergeCell ref="B45:D45"/>
+    <mergeCell ref="BE78:BG78"/>
     <mergeCell ref="BE53:BG53"/>
     <mergeCell ref="AJ60:AL60"/>
     <mergeCell ref="AM32:AO32"/>
@@ -19845,6 +20753,7 @@
     <mergeCell ref="E32:I32"/>
     <mergeCell ref="BH66:BJ66"/>
     <mergeCell ref="AS41:AU41"/>
+    <mergeCell ref="Q78:W78"/>
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
@@ -19860,6 +20769,7 @@
     <mergeCell ref="X41:AD41"/>
     <mergeCell ref="AS43:AU43"/>
     <mergeCell ref="BH68:BJ68"/>
+    <mergeCell ref="AE76:AF76"/>
     <mergeCell ref="AY63:BA63"/>
     <mergeCell ref="BE25:BG25"/>
     <mergeCell ref="BK38:BQ38"/>
@@ -19872,14 +20782,15 @@
     <mergeCell ref="AS36:AU36"/>
     <mergeCell ref="J50:P50"/>
     <mergeCell ref="AM39:AO39"/>
+    <mergeCell ref="AJ78:AL78"/>
     <mergeCell ref="J42:P42"/>
     <mergeCell ref="BK63:BQ63"/>
     <mergeCell ref="AJ15:AL15"/>
     <mergeCell ref="AY67:BA67"/>
-    <mergeCell ref="BB72:BD72"/>
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="AG19:AI19"/>
     <mergeCell ref="X36:AD36"/>
+    <mergeCell ref="AE77:AF77"/>
     <mergeCell ref="Q25:W25"/>
     <mergeCell ref="AV37:AX37"/>
     <mergeCell ref="BB65:BD65"/>
@@ -19912,12 +20823,12 @@
     <mergeCell ref="AM23:AO23"/>
     <mergeCell ref="AE24:AF24"/>
     <mergeCell ref="J70:P70"/>
+    <mergeCell ref="A72:BQ72"/>
     <mergeCell ref="AV27:AX27"/>
     <mergeCell ref="BE55:BG55"/>
     <mergeCell ref="AS31:AU31"/>
     <mergeCell ref="AM71:AO71"/>
     <mergeCell ref="X64:AD64"/>
-    <mergeCell ref="AG72:AI72"/>
     <mergeCell ref="J32:P32"/>
     <mergeCell ref="J63:P63"/>
     <mergeCell ref="AY38:BA38"/>
@@ -19937,6 +20848,7 @@
     <mergeCell ref="BB60:BD60"/>
     <mergeCell ref="B69:D69"/>
     <mergeCell ref="A61:BQ61"/>
+    <mergeCell ref="J76:P76"/>
     <mergeCell ref="AP59:AR59"/>
     <mergeCell ref="E73:I73"/>
     <mergeCell ref="AP46:AR46"/>
@@ -19964,6 +20876,7 @@
     <mergeCell ref="BE74:BG74"/>
     <mergeCell ref="AM47:AO47"/>
     <mergeCell ref="B10:D11"/>
+    <mergeCell ref="AY77:BA77"/>
     <mergeCell ref="J45:P45"/>
     <mergeCell ref="Q35:W35"/>
     <mergeCell ref="AM19:AO19"/>
@@ -19975,14 +20888,14 @@
     <mergeCell ref="AV71:AX71"/>
     <mergeCell ref="E53:I53"/>
     <mergeCell ref="AE70:AF70"/>
-    <mergeCell ref="AY72:BA72"/>
+    <mergeCell ref="BB73:BD73"/>
     <mergeCell ref="AM48:AO48"/>
-    <mergeCell ref="BB73:BD73"/>
     <mergeCell ref="Q74:W74"/>
     <mergeCell ref="Q49:W49"/>
     <mergeCell ref="E68:I68"/>
     <mergeCell ref="BK43:BQ43"/>
     <mergeCell ref="AV73:AX73"/>
+    <mergeCell ref="AV76:AX76"/>
     <mergeCell ref="AF6:AH6"/>
     <mergeCell ref="E55:I55"/>
     <mergeCell ref="AE32:AF32"/>
@@ -20002,8 +20915,8 @@
     <mergeCell ref="AY59:BA59"/>
     <mergeCell ref="AS70:AU70"/>
     <mergeCell ref="J71:P71"/>
-    <mergeCell ref="X72:AD72"/>
     <mergeCell ref="AM73:AO73"/>
+    <mergeCell ref="AV77:AX77"/>
     <mergeCell ref="J58:P58"/>
     <mergeCell ref="AS32:AU32"/>
     <mergeCell ref="AM45:AO45"/>
@@ -20022,6 +20935,7 @@
     <mergeCell ref="AG33:AI33"/>
     <mergeCell ref="X17:AD17"/>
     <mergeCell ref="Q54:W54"/>
+    <mergeCell ref="J77:P77"/>
     <mergeCell ref="AS65:AU65"/>
     <mergeCell ref="AY27:BA27"/>
     <mergeCell ref="AJ31:AL31"/>
@@ -20033,7 +20947,6 @@
     <mergeCell ref="AV66:AX66"/>
     <mergeCell ref="X19:AD19"/>
     <mergeCell ref="AE60:AF60"/>
-    <mergeCell ref="B72:D72"/>
     <mergeCell ref="AS58:AU58"/>
     <mergeCell ref="AG34:AI34"/>
     <mergeCell ref="AV59:AX59"/>
@@ -20059,6 +20972,8 @@
     <mergeCell ref="AG59:AI59"/>
     <mergeCell ref="BK64:BQ64"/>
     <mergeCell ref="J66:P66"/>
+    <mergeCell ref="BE76:BG76"/>
+    <mergeCell ref="AG76:AI76"/>
     <mergeCell ref="BK51:BQ51"/>
     <mergeCell ref="AM67:AO67"/>
     <mergeCell ref="X60:AD60"/>
@@ -20075,6 +20990,7 @@
     <mergeCell ref="AP65:AR65"/>
     <mergeCell ref="AM20:AO20"/>
     <mergeCell ref="AM69:AO69"/>
+    <mergeCell ref="BE77:BG77"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="AY11:BA11"/>
@@ -20083,11 +20999,14 @@
     <mergeCell ref="AS13:AU13"/>
     <mergeCell ref="E69:I69"/>
     <mergeCell ref="AP17:AR17"/>
+    <mergeCell ref="AS78:AU78"/>
     <mergeCell ref="Q42:W42"/>
     <mergeCell ref="A12:BQ12"/>
     <mergeCell ref="AY15:BA15"/>
     <mergeCell ref="AS53:AU53"/>
+    <mergeCell ref="BB76:BD76"/>
     <mergeCell ref="AG23:AI23"/>
+    <mergeCell ref="E77:I77"/>
     <mergeCell ref="X13:AD13"/>
     <mergeCell ref="AS15:AU15"/>
     <mergeCell ref="AE48:AF48"/>
@@ -20107,7 +21026,6 @@
     <mergeCell ref="AG41:AI41"/>
     <mergeCell ref="BH69:BJ69"/>
     <mergeCell ref="AS73:AU73"/>
-    <mergeCell ref="E72:I72"/>
     <mergeCell ref="BH35:BJ35"/>
     <mergeCell ref="AP39:AR39"/>
     <mergeCell ref="AP14:AR14"/>
@@ -20132,6 +21050,7 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="Q70:W70"/>
     <mergeCell ref="AE66:AF66"/>
+    <mergeCell ref="B78:D78"/>
     <mergeCell ref="Q45:W45"/>
     <mergeCell ref="AV69:AX69"/>
     <mergeCell ref="E17:I17"/>
@@ -20165,7 +21084,6 @@
     <mergeCell ref="AV16:AX16"/>
     <mergeCell ref="Q63:W63"/>
     <mergeCell ref="Q50:W50"/>
-    <mergeCell ref="AM72:AO72"/>
     <mergeCell ref="AJ27:AL27"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="AY41:BA41"/>
@@ -20190,12 +21108,13 @@
     <mergeCell ref="BE47:BG47"/>
     <mergeCell ref="AP22:AR22"/>
     <mergeCell ref="BK60:BQ60"/>
+    <mergeCell ref="AP78:AR78"/>
     <mergeCell ref="B38:D38"/>
+    <mergeCell ref="BK78:BQ78"/>
     <mergeCell ref="AJ53:AL53"/>
     <mergeCell ref="AP15:AR15"/>
     <mergeCell ref="AS16:AU16"/>
     <mergeCell ref="AM54:AO54"/>
-    <mergeCell ref="BH72:BJ72"/>
     <mergeCell ref="AV10:BJ10"/>
     <mergeCell ref="BE27:BG27"/>
     <mergeCell ref="J17:P17"/>
@@ -20250,13 +21169,13 @@
     <mergeCell ref="AJ66:AL66"/>
     <mergeCell ref="BE46:BG46"/>
     <mergeCell ref="AG70:AI70"/>
-    <mergeCell ref="AE72:AF72"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
     <mergeCell ref="AP74:AR74"/>
     <mergeCell ref="BK20:BQ20"/>
     <mergeCell ref="AY28:BA28"/>
     <mergeCell ref="B34:D34"/>
+    <mergeCell ref="AJ77:AL77"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="AY64:BA64"/>
     <mergeCell ref="AJ68:AL68"/>
@@ -20292,6 +21211,7 @@
     <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="AJ21:AL21"/>
     <mergeCell ref="J27:P27"/>
+    <mergeCell ref="BB78:BD78"/>
     <mergeCell ref="AG25:AI25"/>
     <mergeCell ref="AY33:BA33"/>
     <mergeCell ref="A52:BQ52"/>
@@ -20315,6 +21235,7 @@
     <mergeCell ref="X75:AD75"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="BK35:BQ35"/>
+    <mergeCell ref="AS77:AU77"/>
     <mergeCell ref="AY39:BA39"/>
     <mergeCell ref="AG53:AI53"/>
     <mergeCell ref="AP34:AR34"/>
@@ -20335,15 +21256,20 @@
     <mergeCell ref="BK74:BQ74"/>
     <mergeCell ref="AM75:AO75"/>
     <mergeCell ref="J38:P38"/>
+    <mergeCell ref="AG78:AI78"/>
     <mergeCell ref="K7:M7"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="Q28:W28"/>
+    <mergeCell ref="AP76:AR76"/>
     <mergeCell ref="BE69:BG69"/>
     <mergeCell ref="AG15:AI15"/>
     <mergeCell ref="AJ16:AL16"/>
     <mergeCell ref="X32:AD32"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="E59:I59"/>
+    <mergeCell ref="AJ76:AL76"/>
+    <mergeCell ref="BK76:BQ76"/>
+    <mergeCell ref="AE78:AF78"/>
     <mergeCell ref="E46:I46"/>
     <mergeCell ref="BE62:BG62"/>
     <mergeCell ref="J15:P15"/>
@@ -20403,8 +21329,8 @@
     <mergeCell ref="B65:D65"/>
     <mergeCell ref="AJ64:AL64"/>
     <mergeCell ref="T7:V7"/>
-    <mergeCell ref="J72:P72"/>
     <mergeCell ref="J28:P28"/>
+    <mergeCell ref="AY78:BA78"/>
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="BK49:BQ49"/>
     <mergeCell ref="AG67:AI67"/>
@@ -20416,6 +21342,7 @@
     <mergeCell ref="AV41:AX41"/>
     <mergeCell ref="AE13:AF13"/>
     <mergeCell ref="AS45:AU45"/>
+    <mergeCell ref="X78:AD78"/>
     <mergeCell ref="AG69:AI69"/>
     <mergeCell ref="X53:AD53"/>
     <mergeCell ref="X47:AD47"/>
@@ -20443,16 +21370,14 @@
     <mergeCell ref="AY71:BA71"/>
     <mergeCell ref="E62:I62"/>
     <mergeCell ref="J56:P56"/>
-    <mergeCell ref="BE72:BG72"/>
     <mergeCell ref="AY58:BA58"/>
     <mergeCell ref="AS71:AU71"/>
     <mergeCell ref="J43:P43"/>
     <mergeCell ref="X25:AD25"/>
     <mergeCell ref="BB69:BD69"/>
     <mergeCell ref="AG16:AI16"/>
-    <mergeCell ref="AV72:AX72"/>
+    <mergeCell ref="AY73:BA73"/>
     <mergeCell ref="E64:I64"/>
-    <mergeCell ref="AY73:BA73"/>
     <mergeCell ref="X71:AD71"/>
     <mergeCell ref="E51:I51"/>
     <mergeCell ref="BK31:BQ31"/>
@@ -20462,6 +21387,7 @@
     <mergeCell ref="BB21:BD21"/>
     <mergeCell ref="N6:P6"/>
     <mergeCell ref="AM25:AO25"/>
+    <mergeCell ref="BH78:BJ78"/>
     <mergeCell ref="E65:I65"/>
     <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
@@ -20488,15 +21414,16 @@
     <mergeCell ref="B58:D58"/>
     <mergeCell ref="E75:I75"/>
     <mergeCell ref="BE60:BG60"/>
+    <mergeCell ref="AG77:AI77"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE17 AE19:AE25 AE27:AE29 AE31:AE39 AE41:AE43 AE45:AE51 AE53:AE56 AE58:AE60 AE62:AE75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE17 AE19:AE25 AE27:AE29 AE31:AE39 AE41:AE43 AE45:AE51 AE53:AE56 AE58:AE60 AE62:AE71 AE73:AE78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG17 AG19:AG25 AG27:AG29 AG31:AG39 AG41:AG43 AG45:AG51 AG53:AG56 AG58:AG60 AG62:AG75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG17 AG19:AG25 AG27:AG29 AG31:AG39 AG41:AG43 AG45:AG51 AG53:AG56 AG58:AG60 AG62:AG71 AG73:AG78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV17 AV19:AV25 AV27:AV29 AV31:AV39 AV41:AV43 AV45:AV51 AV53:AV56 AV58:AV60 AV62:AV75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV17 AV19:AV25 AV27:AV29 AV31:AV39 AV41:AV43 AV45:AV51 AV53:AV56 AV58:AV60 AV62:AV71 AV73:AV78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者Excelデータ取込画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-016/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者Excelデータ取込画面_v1.0.xlsx
@@ -11743,7 +11743,7 @@
       <c r="BP35" s="10" t="n"/>
       <c r="BQ35" s="11" t="n"/>
     </row>
-    <row r="36" ht="400" customHeight="1">
+    <row r="36" ht="384" customHeight="1">
       <c r="A36" s="44" t="n">
         <v>21</v>
       </c>
@@ -11756,7 +11756,7 @@
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="46" t="inlineStr">
         <is>
-          <t>30001行以上のデータ — 行数上限超過</t>
+          <t>5001行以上のデータ — 行数上限超過</t>
         </is>
       </c>
       <c r="F36" s="10" t="n"/>
@@ -11767,7 +11767,7 @@
         <is>
           <t>・role: JA_HONTEN
 ・ログイン済 + MFA認証済
-・テストファイル：30001行のデータを含む `.xlsx`</t>
+・テストファイル：5001行のデータを含む `.xlsx`</t>
         </is>
       </c>
       <c r="K36" s="10" t="n"/>
@@ -11792,7 +11792,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Excelファイル選択ボタン押下、30001行ファイルを選択
+            <t xml:space="preserve">Excelファイル選択ボタン押下、5001行ファイルを選択
 </t>
           </r>
           <r>
@@ -11869,7 +11869,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">プレビューに30001行が表示されること（または上限超過の案内が表示されること）
+            <t xml:space="preserve">プレビューに5001行が表示されること（または上限超過の案内が表示されること）
 </t>
           </r>
           <r>
@@ -11886,7 +11886,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">トースト `ファイルの行数が上限（30000行）を超えているため、取込みできません。` が表示されること（ACSMS-MSG-016-006）、サーバーへのリクエストが送信されないこと
+            <t xml:space="preserve">トースト `ファイルの行数が上限（5000行）を超えているため、取込みできません。` が表示されること（ACSMS-MSG-016-006）、サーバーへのリクエストが送信されないこと
 </t>
           </r>
           <r>
@@ -11903,7 +11903,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・上限30000行（境界値：30000行は取込可能、30001行は不可）
+            <t xml:space="preserve">・上限5000行（境界値：5000行は取込可能、5001行は不可）
 </t>
           </r>
           <r>
@@ -17535,7 +17535,7 @@
       <c r="D68" s="11" t="n"/>
       <c r="E68" s="46" t="inlineStr">
         <is>
-          <t>サーバー側 ROW_LIMIT_EXCEEDED — 30001行送信</t>
+          <t>サーバー側 ROW_LIMIT_EXCEEDED — 5001行送信</t>
         </is>
       </c>
       <c r="F68" s="10" t="n"/>
@@ -17570,7 +17570,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>DevTools で POST `/api/v1/dokusya/import` を `rows: [...30001 items...]` で送信</t>
+            <t>DevTools で POST `/api/v1/dokusya/import` を `rows: [...5001 items...]` で送信</t>
           </r>
         </is>
       </c>
@@ -17596,7 +17596,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: ROW_LIMIT_EXCEEDED`、メッセージ `ファイルの行数が上限（30000行）を超えているため、取込みできません。`）、DB が変更されないこと
+            <t xml:space="preserve">HTTPステータスコード400が返却されること（`error_code: ROW_LIMIT_EXCEEDED`、メッセージ `ファイルの行数が上限（5000行）を超えているため、取込みできません。`）、DB が変更されないこと
 </t>
           </r>
           <r>
@@ -17613,15 +17613,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・サーバー側で 30000 行上限を再チェック（クライアント側回避防止）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・境界値：30000行は取込可能、30001行は不可</t>
+            <t xml:space="preserve">・サーバー側で 5000 行上限を再チェック（クライアント側回避防止）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・境界値：5000行は取込可能、5001行は不可</t>
           </r>
         </is>
       </c>
